--- a/PLANEACION_SEMANAL 1.xlsx
+++ b/PLANEACION_SEMANAL 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chanitosfrutas.sharepoint.com/sites/04.Logstica/Documentos compartidos/General/Pre-enfrío/09. Desarrollos/Planeacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="360" documentId="8_{545E5EC0-B69F-4327-BF2C-9EFD71AFF5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFC63D41-862F-4575-8A1A-84021D729616}"/>
+  <xr:revisionPtr revIDLastSave="374" documentId="8_{545E5EC0-B69F-4327-BF2C-9EFD71AFF5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E92436E1-3592-4698-9C14-C2A2242CA560}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D41B2D9D-66D1-4881-AE1E-852E308D9588}"/>
   </bookViews>
@@ -17,6 +17,9 @@
     <sheet name="UBICACIONES" sheetId="4" r:id="rId2"/>
     <sheet name="CATALOGO" sheetId="3" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PLANEACION!$A$1:$M$135</definedName>
   </definedNames>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3029" uniqueCount="1438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3809" uniqueCount="1522">
   <si>
     <t>Descripción</t>
   </si>
@@ -4364,6 +4367,258 @@
   </si>
   <si>
     <t>A04 017 Rancho Nuevo</t>
+  </si>
+  <si>
+    <t>A11045-370709-1</t>
+  </si>
+  <si>
+    <t>A01002-370709-1</t>
+  </si>
+  <si>
+    <t>A01002-370709-4</t>
+  </si>
+  <si>
+    <t>A01002-370709-3</t>
+  </si>
+  <si>
+    <t>A01002-370709-5</t>
+  </si>
+  <si>
+    <t>A01001-370709-1</t>
+  </si>
+  <si>
+    <t>A01001-370709-4</t>
+  </si>
+  <si>
+    <t>A01001-370709-3</t>
+  </si>
+  <si>
+    <t>A01001-370709-5</t>
+  </si>
+  <si>
+    <t>A01003-370709-1</t>
+  </si>
+  <si>
+    <t>A01003-370709-4</t>
+  </si>
+  <si>
+    <t>A01003-370709-3</t>
+  </si>
+  <si>
+    <t>A01003-370709-5</t>
+  </si>
+  <si>
+    <t>A11045-370809-1</t>
+  </si>
+  <si>
+    <t>A04084-370809-1</t>
+  </si>
+  <si>
+    <t>A04039-370809-1</t>
+  </si>
+  <si>
+    <t>A01001-370809-1</t>
+  </si>
+  <si>
+    <t>A01001-370809-4</t>
+  </si>
+  <si>
+    <t>A01001-370809-3</t>
+  </si>
+  <si>
+    <t>A01001-370809-5</t>
+  </si>
+  <si>
+    <t>A41100-370809-1</t>
+  </si>
+  <si>
+    <t>A01003-370809-1</t>
+  </si>
+  <si>
+    <t>A01003-370809-4</t>
+  </si>
+  <si>
+    <t>A01003-370809-3</t>
+  </si>
+  <si>
+    <t>A01003-370809-5</t>
+  </si>
+  <si>
+    <t>A01002-370809-1</t>
+  </si>
+  <si>
+    <t>A01002-370809-4</t>
+  </si>
+  <si>
+    <t>A01002-370809-3</t>
+  </si>
+  <si>
+    <t>A01002-370809-5</t>
+  </si>
+  <si>
+    <t>A11045-370909-1</t>
+  </si>
+  <si>
+    <t>A04084-370909-1</t>
+  </si>
+  <si>
+    <t>A04039-370909-1</t>
+  </si>
+  <si>
+    <t>A01002-370909-1</t>
+  </si>
+  <si>
+    <t>A01002-370909-4</t>
+  </si>
+  <si>
+    <t>A01002-370909-3</t>
+  </si>
+  <si>
+    <t>A01002-370909-5</t>
+  </si>
+  <si>
+    <t>A01004-370909-1</t>
+  </si>
+  <si>
+    <t>A01004-370909-4</t>
+  </si>
+  <si>
+    <t>A01004-370909-3</t>
+  </si>
+  <si>
+    <t>A01004-370909-5</t>
+  </si>
+  <si>
+    <t>A01001-370909-1</t>
+  </si>
+  <si>
+    <t>A01001-370909-4</t>
+  </si>
+  <si>
+    <t>A01001-370909-3</t>
+  </si>
+  <si>
+    <t>A01001-370909-5</t>
+  </si>
+  <si>
+    <t>A04084-371009-1</t>
+  </si>
+  <si>
+    <t>A04039-371009-1</t>
+  </si>
+  <si>
+    <t>A04037-371009-1</t>
+  </si>
+  <si>
+    <t>A06043-371009-1</t>
+  </si>
+  <si>
+    <t>A01003-371009-1</t>
+  </si>
+  <si>
+    <t>A01003-371009-4</t>
+  </si>
+  <si>
+    <t>A01003-371009-3</t>
+  </si>
+  <si>
+    <t>A01003-371009-5</t>
+  </si>
+  <si>
+    <t>A01001-371009-1</t>
+  </si>
+  <si>
+    <t>A01001-371009-4</t>
+  </si>
+  <si>
+    <t>A01001-371009-3</t>
+  </si>
+  <si>
+    <t>A01001-371009-5</t>
+  </si>
+  <si>
+    <t>A01002-371009-1</t>
+  </si>
+  <si>
+    <t>A01002-371009-4</t>
+  </si>
+  <si>
+    <t>A01002-371009-3</t>
+  </si>
+  <si>
+    <t>A01002-371009-5</t>
+  </si>
+  <si>
+    <t>A04084-371109-1</t>
+  </si>
+  <si>
+    <t>A06043-371109-1</t>
+  </si>
+  <si>
+    <t>A27073-371109-1</t>
+  </si>
+  <si>
+    <t>A01003-371109-1</t>
+  </si>
+  <si>
+    <t>A01002-371109-1</t>
+  </si>
+  <si>
+    <t>A01001-371109-1</t>
+  </si>
+  <si>
+    <t>A01003-371109-4</t>
+  </si>
+  <si>
+    <t>A01003-371109-3</t>
+  </si>
+  <si>
+    <t>A01003-371109-5</t>
+  </si>
+  <si>
+    <t>A01001-371109-4</t>
+  </si>
+  <si>
+    <t>A01001-371109-3</t>
+  </si>
+  <si>
+    <t>A01001-371109-5</t>
+  </si>
+  <si>
+    <t>A01002-371109-4</t>
+  </si>
+  <si>
+    <t>A01002-371109-3</t>
+  </si>
+  <si>
+    <t>A01002-371109-5</t>
+  </si>
+  <si>
+    <t>A04037-371209-1</t>
+  </si>
+  <si>
+    <t>A01004-371209-1</t>
+  </si>
+  <si>
+    <t>A01004-371209-4</t>
+  </si>
+  <si>
+    <t>A01004-371209-3</t>
+  </si>
+  <si>
+    <t>A01004-371209-5</t>
+  </si>
+  <si>
+    <t>A01002-371209-1</t>
+  </si>
+  <si>
+    <t>A01002-371209-4</t>
+  </si>
+  <si>
+    <t>A01002-371209-3</t>
+  </si>
+  <si>
+    <t>A01002-371209-5</t>
   </si>
 </sst>
 </file>
@@ -4895,7 +5150,17 @@
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4924,6 +5189,39 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="organico"/>
+      <sheetName val="s-37"/>
+      <sheetName val="Tulti-CEDA org"/>
+      <sheetName val="fincas"/>
+      <sheetName val="Tarimas"/>
+      <sheetName val="Indicadores"/>
+      <sheetName val="trasbordo"/>
+      <sheetName val="Resultados_OV_S37"/>
+      <sheetName val="Bitacora"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5270,7 +5568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6943C4E-D0C1-4399-9277-8C3BA29014B7}">
-  <dimension ref="A1:M160"/>
+  <dimension ref="A1:M304"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" style="6" customWidth="1"/>
@@ -12318,10 +12616,6358 @@
         <v>46272</v>
       </c>
     </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A161" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B161" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C161" s="17" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D161" t="s">
+        <v>15</v>
+      </c>
+      <c r="E161" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F161" s="6">
+        <f>+VLOOKUP(E161,CATALOGO!G:L,6,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G161" s="14">
+        <v>960</v>
+      </c>
+      <c r="H161" s="14">
+        <v>20</v>
+      </c>
+      <c r="I161" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J161" s="12">
+        <v>37</v>
+      </c>
+      <c r="K161">
+        <f>+IF(E161="","",VLOOKUP(E161,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L161">
+        <f>+IF(E161="","",VLOOKUP(E161,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M161" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A162" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B162" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C162" s="17" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D162" t="s">
+        <v>15</v>
+      </c>
+      <c r="E162" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F162" s="6">
+        <f>+VLOOKUP(E162,CATALOGO!G:L,6,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G162" s="14">
+        <v>960</v>
+      </c>
+      <c r="H162" s="14">
+        <v>20</v>
+      </c>
+      <c r="I162" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J162" s="12">
+        <v>37</v>
+      </c>
+      <c r="K162">
+        <f>+IF(E162="","",VLOOKUP(E162,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L162">
+        <f>+IF(E162="","",VLOOKUP(E162,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M162" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A163" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B163" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C163" s="17" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D163" t="s">
+        <v>17</v>
+      </c>
+      <c r="E163" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F163" s="6">
+        <f>+VLOOKUP(E163,CATALOGO!G:L,6,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G163" s="14">
+        <v>240</v>
+      </c>
+      <c r="H163" s="14">
+        <v>5</v>
+      </c>
+      <c r="I163" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J163" s="12">
+        <v>37</v>
+      </c>
+      <c r="K163">
+        <f>+IF(E163="","",VLOOKUP(E163,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L163">
+        <f>+IF(E163="","",VLOOKUP(E163,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M163" s="15">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A164" s="88" t="s">
+        <v>18</v>
+      </c>
+      <c r="B164" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C164" s="17" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D164" t="s">
+        <v>17</v>
+      </c>
+      <c r="E164" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="F164" s="6">
+        <f>+VLOOKUP(E164,CATALOGO!G:L,6,0)</f>
+        <v>6</v>
+      </c>
+      <c r="G164" s="14">
+        <v>48</v>
+      </c>
+      <c r="H164" s="14">
+        <v>1</v>
+      </c>
+      <c r="I164" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J164" s="12">
+        <v>37</v>
+      </c>
+      <c r="K164">
+        <f>+IF(E164="","",VLOOKUP(E164,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L164">
+        <f>+IF(E164="","",VLOOKUP(E164,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M164" s="15">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A165" s="88" t="s">
+        <v>21</v>
+      </c>
+      <c r="B165" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C165" s="17" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D165" t="s">
+        <v>17</v>
+      </c>
+      <c r="E165" s="88" t="s">
+        <v>23</v>
+      </c>
+      <c r="F165" s="6">
+        <f>+VLOOKUP(E165,CATALOGO!G:L,6,0)</f>
+        <v>5</v>
+      </c>
+      <c r="G165" s="14">
+        <v>84</v>
+      </c>
+      <c r="H165" s="14">
+        <v>1.75</v>
+      </c>
+      <c r="I165" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J165" s="12">
+        <v>37</v>
+      </c>
+      <c r="K165">
+        <f>+IF(E165="","",VLOOKUP(E165,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L165">
+        <f>+IF(E165="","",VLOOKUP(E165,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M165" s="15">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A166" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B166" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C166" s="17" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D166" t="s">
+        <v>17</v>
+      </c>
+      <c r="E166" s="88" t="s">
+        <v>23</v>
+      </c>
+      <c r="F166" s="6">
+        <f>+VLOOKUP(E166,CATALOGO!G:L,6,0)</f>
+        <v>5</v>
+      </c>
+      <c r="G166" s="14">
+        <v>204</v>
+      </c>
+      <c r="H166" s="14">
+        <v>4</v>
+      </c>
+      <c r="I166" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J166" s="12">
+        <v>37</v>
+      </c>
+      <c r="K166">
+        <f>+IF(E166="","",VLOOKUP(E166,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L166">
+        <f>+IF(E166="","",VLOOKUP(E166,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M166" s="15">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A167" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B167" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C167" s="17" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D167" t="s">
+        <v>17</v>
+      </c>
+      <c r="E167" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="F167" s="6">
+        <f>+VLOOKUP(E167,CATALOGO!G:L,6,0)</f>
+        <v>3</v>
+      </c>
+      <c r="G167" s="14">
+        <f>1152-240-48-84-204-96</f>
+        <v>480</v>
+      </c>
+      <c r="H167" s="14">
+        <v>10</v>
+      </c>
+      <c r="I167" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J167" s="12">
+        <v>37</v>
+      </c>
+      <c r="K167">
+        <f>+IF(E167="","",VLOOKUP(E167,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L167">
+        <f>+IF(E167="","",VLOOKUP(E167,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M167" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A168" s="88" t="s">
+        <v>18</v>
+      </c>
+      <c r="B168" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C168" s="17" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D168" t="s">
+        <v>17</v>
+      </c>
+      <c r="E168" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="F168" s="6">
+        <f>+VLOOKUP(E168,CATALOGO!G:L,6,0)</f>
+        <v>3</v>
+      </c>
+      <c r="G168" s="14">
+        <v>96</v>
+      </c>
+      <c r="H168" s="14">
+        <v>2</v>
+      </c>
+      <c r="I168" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J168" s="12">
+        <v>37</v>
+      </c>
+      <c r="K168">
+        <f>+IF(E168="","",VLOOKUP(E168,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L168">
+        <f>+IF(E168="","",VLOOKUP(E168,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M168" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A169" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B169" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C169" s="17" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D169" t="s">
+        <v>17</v>
+      </c>
+      <c r="E169" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="F169" s="6">
+        <f>+VLOOKUP(E169,CATALOGO!G:L,6,0)</f>
+        <v>6</v>
+      </c>
+      <c r="G169" s="14">
+        <v>96</v>
+      </c>
+      <c r="H169" s="14">
+        <v>2</v>
+      </c>
+      <c r="I169" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J169" s="12">
+        <v>37</v>
+      </c>
+      <c r="K169">
+        <f>+IF(E169="","",VLOOKUP(E169,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L169">
+        <f>+IF(E169="","",VLOOKUP(E169,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M169" s="15">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A170" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B170" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C170" s="17" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D170" t="s">
+        <v>17</v>
+      </c>
+      <c r="E170" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F170" s="6">
+        <f>+VLOOKUP(E170,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G170" s="14">
+        <v>10</v>
+      </c>
+      <c r="H170" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I170" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J170" s="12">
+        <v>37</v>
+      </c>
+      <c r="K170">
+        <f>+IF(E170="","",VLOOKUP(E170,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L170">
+        <f>+IF(E170="","",VLOOKUP(E170,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M170" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A171" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B171" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C171" s="17" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D171" t="s">
+        <v>17</v>
+      </c>
+      <c r="E171" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F171" s="6">
+        <f>+VLOOKUP(E171,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G171" s="14">
+        <v>48</v>
+      </c>
+      <c r="H171" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I171" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J171" s="12">
+        <v>37</v>
+      </c>
+      <c r="K171">
+        <f>+IF(E171="","",VLOOKUP(E171,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L171">
+        <f>+IF(E171="","",VLOOKUP(E171,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M171" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A172" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B172" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C172" s="17" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D172" t="s">
+        <v>17</v>
+      </c>
+      <c r="E172" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F172" s="6">
+        <f>+VLOOKUP(E172,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G172" s="14">
+        <v>63</v>
+      </c>
+      <c r="H172" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I172" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J172" s="12">
+        <v>37</v>
+      </c>
+      <c r="K172">
+        <f>+IF(E172="","",VLOOKUP(E172,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L172">
+        <f>+IF(E172="","",VLOOKUP(E172,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M172" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A173" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B173" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C173" s="17" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D173" t="s">
+        <v>17</v>
+      </c>
+      <c r="E173" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F173" s="6">
+        <f>+VLOOKUP(E173,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G173" s="14">
+        <v>20</v>
+      </c>
+      <c r="H173" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I173" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J173" s="12">
+        <v>37</v>
+      </c>
+      <c r="K173">
+        <f>+IF(E173="","",VLOOKUP(E173,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L173">
+        <f>+IF(E173="","",VLOOKUP(E173,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M173" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A174" s="88" t="s">
+        <v>21</v>
+      </c>
+      <c r="B174" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C174" s="17" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D174" t="s">
+        <v>37</v>
+      </c>
+      <c r="E174" s="88" t="s">
+        <v>23</v>
+      </c>
+      <c r="F174" s="6">
+        <f>+VLOOKUP(E174,CATALOGO!G:L,6,0)</f>
+        <v>5</v>
+      </c>
+      <c r="G174" s="14">
+        <f>66+18</f>
+        <v>84</v>
+      </c>
+      <c r="H174" s="14">
+        <v>1.75</v>
+      </c>
+      <c r="I174" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J174" s="12">
+        <v>37</v>
+      </c>
+      <c r="K174">
+        <f>+IF(E174="","",VLOOKUP(E174,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L174">
+        <f>+IF(E174="","",VLOOKUP(E174,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M174" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A175" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B175" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C175" s="17" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D175" t="s">
+        <v>37</v>
+      </c>
+      <c r="E175" s="88" t="s">
+        <v>23</v>
+      </c>
+      <c r="F175" s="6">
+        <f>+VLOOKUP(E175,CATALOGO!G:L,6,0)</f>
+        <v>5</v>
+      </c>
+      <c r="G175" s="14">
+        <f>1086-18</f>
+        <v>1068</v>
+      </c>
+      <c r="H175" s="14">
+        <v>22.25</v>
+      </c>
+      <c r="I175" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J175" s="12">
+        <v>37</v>
+      </c>
+      <c r="K175">
+        <f>+IF(E175="","",VLOOKUP(E175,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L175">
+        <f>+IF(E175="","",VLOOKUP(E175,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M175" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A176" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B176" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C176" s="17" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D176" t="s">
+        <v>37</v>
+      </c>
+      <c r="E176" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="F176" s="6">
+        <f>+VLOOKUP(E176,CATALOGO!G:L,6,0)</f>
+        <v>6</v>
+      </c>
+      <c r="G176" s="14">
+        <v>96</v>
+      </c>
+      <c r="H176" s="14">
+        <v>2</v>
+      </c>
+      <c r="I176" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J176" s="12">
+        <v>37</v>
+      </c>
+      <c r="K176">
+        <f>+IF(E176="","",VLOOKUP(E176,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L176">
+        <f>+IF(E176="","",VLOOKUP(E176,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M176" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A177" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B177" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C177" s="17" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D177" t="s">
+        <v>37</v>
+      </c>
+      <c r="E177" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F177" s="6">
+        <f>+VLOOKUP(E177,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G177" s="14">
+        <v>84</v>
+      </c>
+      <c r="H177" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I177" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J177" s="12">
+        <v>37</v>
+      </c>
+      <c r="K177">
+        <f>+IF(E177="","",VLOOKUP(E177,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L177">
+        <f>+IF(E177="","",VLOOKUP(E177,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M177" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A178" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B178" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C178" s="17" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D178" t="s">
+        <v>37</v>
+      </c>
+      <c r="E178" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F178" s="6">
+        <f>+VLOOKUP(E178,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G178" s="14">
+        <v>88</v>
+      </c>
+      <c r="H178" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I178" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J178" s="12">
+        <v>37</v>
+      </c>
+      <c r="K178">
+        <f>+IF(E178="","",VLOOKUP(E178,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L178">
+        <f>+IF(E178="","",VLOOKUP(E178,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M178" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A179" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B179" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C179" s="17" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D179" t="s">
+        <v>37</v>
+      </c>
+      <c r="E179" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F179" s="6">
+        <f>+VLOOKUP(E179,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G179" s="14">
+        <v>29</v>
+      </c>
+      <c r="H179" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I179" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J179" s="12">
+        <v>37</v>
+      </c>
+      <c r="K179">
+        <f>+IF(E179="","",VLOOKUP(E179,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L179">
+        <f>+IF(E179="","",VLOOKUP(E179,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M179" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A180" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B180" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C180" s="17" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D180" t="s">
+        <v>37</v>
+      </c>
+      <c r="E180" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F180" s="6">
+        <f>+VLOOKUP(E180,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G180" s="14">
+        <v>48</v>
+      </c>
+      <c r="H180" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I180" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J180" s="12">
+        <v>37</v>
+      </c>
+      <c r="K180">
+        <f>+IF(E180="","",VLOOKUP(E180,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L180">
+        <f>+IF(E180="","",VLOOKUP(E180,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M180" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A181" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B181" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C181" s="17" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D181" t="s">
+        <v>38</v>
+      </c>
+      <c r="E181" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="F181" s="6">
+        <f>+VLOOKUP(E181,CATALOGO!G:L,6,0)</f>
+        <v>3</v>
+      </c>
+      <c r="G181" s="14">
+        <v>432</v>
+      </c>
+      <c r="H181" s="14">
+        <v>9</v>
+      </c>
+      <c r="I181" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J181" s="12">
+        <v>37</v>
+      </c>
+      <c r="K181">
+        <f>+IF(E181="","",VLOOKUP(E181,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L181">
+        <f>+IF(E181="","",VLOOKUP(E181,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M181" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A182" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B182" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C182" s="17" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D182" t="s">
+        <v>38</v>
+      </c>
+      <c r="E182" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F182" s="6">
+        <f>+VLOOKUP(E182,CATALOGO!G:L,6,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G182" s="14">
+        <v>960</v>
+      </c>
+      <c r="H182" s="14">
+        <v>20</v>
+      </c>
+      <c r="I182" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J182" s="12">
+        <v>37</v>
+      </c>
+      <c r="K182">
+        <f>+IF(E182="","",VLOOKUP(E182,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L182">
+        <f>+IF(E182="","",VLOOKUP(E182,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M182" s="15">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A183" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B183" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C183" s="17" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D183" t="s">
+        <v>38</v>
+      </c>
+      <c r="E183" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F183" s="6">
+        <f>+VLOOKUP(E183,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G183" s="14">
+        <v>74</v>
+      </c>
+      <c r="H183" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I183" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J183" s="12">
+        <v>37</v>
+      </c>
+      <c r="K183">
+        <f>+IF(E183="","",VLOOKUP(E183,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L183">
+        <f>+IF(E183="","",VLOOKUP(E183,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M183" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A184" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B184" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C184" s="17" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D184" t="s">
+        <v>38</v>
+      </c>
+      <c r="E184" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F184" s="6">
+        <f>+VLOOKUP(E184,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G184" s="14">
+        <v>27</v>
+      </c>
+      <c r="H184" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I184" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J184" s="12">
+        <v>37</v>
+      </c>
+      <c r="K184">
+        <f>+IF(E184="","",VLOOKUP(E184,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L184">
+        <f>+IF(E184="","",VLOOKUP(E184,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M184" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A185" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B185" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C185" s="17" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D185" t="s">
+        <v>38</v>
+      </c>
+      <c r="E185" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F185" s="6">
+        <f>+VLOOKUP(E185,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G185" s="14">
+        <v>30</v>
+      </c>
+      <c r="H185" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I185" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J185" s="12">
+        <v>37</v>
+      </c>
+      <c r="K185">
+        <f>+IF(E185="","",VLOOKUP(E185,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L185">
+        <f>+IF(E185="","",VLOOKUP(E185,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M185" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A186" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B186" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C186" s="17" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D186" t="s">
+        <v>38</v>
+      </c>
+      <c r="E186" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F186" s="6">
+        <f>+VLOOKUP(E186,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G186" s="14">
+        <v>92</v>
+      </c>
+      <c r="H186" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I186" s="16">
+        <v>46272</v>
+      </c>
+      <c r="J186" s="12">
+        <v>37</v>
+      </c>
+      <c r="K186">
+        <f>+IF(E186="","",VLOOKUP(E186,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L186">
+        <f>+IF(E186="","",VLOOKUP(E186,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M186" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A187" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B187" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C187" s="17" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D187" t="s">
+        <v>15</v>
+      </c>
+      <c r="E187" s="88" t="s">
+        <v>39</v>
+      </c>
+      <c r="F187" s="6">
+        <f>+VLOOKUP(E187,CATALOGO!G:L,6,0)</f>
+        <v>4</v>
+      </c>
+      <c r="G187" s="14">
+        <v>624</v>
+      </c>
+      <c r="H187" s="14">
+        <v>13</v>
+      </c>
+      <c r="I187" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J187" s="12">
+        <v>37</v>
+      </c>
+      <c r="K187">
+        <f>+IF(E187="","",VLOOKUP(E187,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L187">
+        <f>+IF(E187="","",VLOOKUP(E187,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M187" s="15">
+        <v>46278</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A188" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B188" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C188" s="17" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D188" t="s">
+        <v>40</v>
+      </c>
+      <c r="E188" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F188" s="6">
+        <f>+VLOOKUP(E188,CATALOGO!G:L,6,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G188" s="14">
+        <v>960</v>
+      </c>
+      <c r="H188" s="14">
+        <v>20</v>
+      </c>
+      <c r="I188" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J188" s="12">
+        <v>37</v>
+      </c>
+      <c r="K188">
+        <f>+IF(E188="","",VLOOKUP(E188,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L188">
+        <f>+IF(E188="","",VLOOKUP(E188,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M188" s="15">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A189" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B189" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C189" s="17" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D189" t="s">
+        <v>41</v>
+      </c>
+      <c r="E189" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F189" s="6">
+        <f>+VLOOKUP(E189,CATALOGO!G:L,6,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G189" s="14">
+        <v>960</v>
+      </c>
+      <c r="H189" s="14">
+        <v>20</v>
+      </c>
+      <c r="I189" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J189" s="12">
+        <v>37</v>
+      </c>
+      <c r="K189">
+        <f>+IF(E189="","",VLOOKUP(E189,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L189">
+        <f>+IF(E189="","",VLOOKUP(E189,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M189" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A190" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="B190" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C190" s="17" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D190" t="s">
+        <v>41</v>
+      </c>
+      <c r="E190" s="88" t="s">
+        <v>44</v>
+      </c>
+      <c r="F190" s="6">
+        <f>+VLOOKUP(E190,CATALOGO!G:L,6,0)</f>
+        <v>1</v>
+      </c>
+      <c r="G190" s="14">
+        <v>480</v>
+      </c>
+      <c r="H190" s="14">
+        <v>10</v>
+      </c>
+      <c r="I190" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J190" s="12">
+        <v>37</v>
+      </c>
+      <c r="K190">
+        <f>+IF(E190="","",VLOOKUP(E190,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L190">
+        <f>+IF(E190="","",VLOOKUP(E190,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M190" s="15">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A191" s="88" t="s">
+        <v>45</v>
+      </c>
+      <c r="B191" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C191" s="17" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D191" t="s">
+        <v>37</v>
+      </c>
+      <c r="E191" s="88" t="s">
+        <v>47</v>
+      </c>
+      <c r="F191" s="6">
+        <f>+VLOOKUP(E191,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G191" s="14">
+        <v>810</v>
+      </c>
+      <c r="H191" s="14">
+        <v>15</v>
+      </c>
+      <c r="I191" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J191" s="12">
+        <v>37</v>
+      </c>
+      <c r="K191">
+        <f>+IF(E191="","",VLOOKUP(E191,CATALOGO!G:I,2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="L191">
+        <f>+IF(E191="","",VLOOKUP(E191,CATALOGO!G:I,3,0))</f>
+        <v>48</v>
+      </c>
+      <c r="M191" s="15">
+        <v>46278</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A192" s="88" t="s">
+        <v>48</v>
+      </c>
+      <c r="B192" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C192" s="17" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D192" t="s">
+        <v>37</v>
+      </c>
+      <c r="E192" s="88" t="s">
+        <v>47</v>
+      </c>
+      <c r="F192" s="6">
+        <f>+VLOOKUP(E192,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G192" s="14">
+        <v>270</v>
+      </c>
+      <c r="H192" s="14">
+        <v>5</v>
+      </c>
+      <c r="I192" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J192" s="12">
+        <v>37</v>
+      </c>
+      <c r="K192">
+        <f>+IF(E192="","",VLOOKUP(E192,CATALOGO!G:I,2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="L192">
+        <f>+IF(E192="","",VLOOKUP(E192,CATALOGO!G:I,3,0))</f>
+        <v>48</v>
+      </c>
+      <c r="M192" s="15">
+        <v>46278</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A193" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B193" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C193" s="17" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D193" t="s">
+        <v>37</v>
+      </c>
+      <c r="E193" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="F193" s="6">
+        <f>+VLOOKUP(E193,CATALOGO!G:L,6,0)</f>
+        <v>6</v>
+      </c>
+      <c r="G193" s="14">
+        <v>240</v>
+      </c>
+      <c r="H193" s="14">
+        <v>5</v>
+      </c>
+      <c r="I193" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J193" s="12">
+        <v>37</v>
+      </c>
+      <c r="K193">
+        <f>+IF(E193="","",VLOOKUP(E193,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L193">
+        <f>+IF(E193="","",VLOOKUP(E193,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M193" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A194" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B194" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C194" s="17" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D194" t="s">
+        <v>37</v>
+      </c>
+      <c r="E194" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F194" s="6">
+        <f>+VLOOKUP(E194,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G194" s="14">
+        <v>53</v>
+      </c>
+      <c r="H194" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I194" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J194" s="12">
+        <v>37</v>
+      </c>
+      <c r="K194">
+        <f>+IF(E194="","",VLOOKUP(E194,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L194">
+        <f>+IF(E194="","",VLOOKUP(E194,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M194" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A195" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B195" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C195" s="17" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D195" t="s">
+        <v>37</v>
+      </c>
+      <c r="E195" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F195" s="6">
+        <f>+VLOOKUP(E195,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G195" s="14">
+        <v>68</v>
+      </c>
+      <c r="H195" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I195" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J195" s="12">
+        <v>37</v>
+      </c>
+      <c r="K195">
+        <f>+IF(E195="","",VLOOKUP(E195,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L195">
+        <f>+IF(E195="","",VLOOKUP(E195,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M195" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A196" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B196" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C196" s="17" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D196" t="s">
+        <v>37</v>
+      </c>
+      <c r="E196" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F196" s="6">
+        <f>+VLOOKUP(E196,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G196" s="14">
+        <v>9</v>
+      </c>
+      <c r="H196" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I196" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J196" s="12">
+        <v>37</v>
+      </c>
+      <c r="K196">
+        <f>+IF(E196="","",VLOOKUP(E196,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L196">
+        <f>+IF(E196="","",VLOOKUP(E196,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M196" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A197" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B197" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C197" s="17" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D197" t="s">
+        <v>37</v>
+      </c>
+      <c r="E197" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F197" s="6">
+        <f>+VLOOKUP(E197,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G197" s="14">
+        <v>38</v>
+      </c>
+      <c r="H197" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I197" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J197" s="12">
+        <v>37</v>
+      </c>
+      <c r="K197">
+        <f>+IF(E197="","",VLOOKUP(E197,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L197">
+        <f>+IF(E197="","",VLOOKUP(E197,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M197" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A198" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="B198" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C198" s="17" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D198" t="s">
+        <v>52</v>
+      </c>
+      <c r="E198" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F198" s="6">
+        <f>+VLOOKUP(E198,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G198" s="14">
+        <v>144</v>
+      </c>
+      <c r="H198" s="14">
+        <v>3</v>
+      </c>
+      <c r="I198" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J198" s="12">
+        <v>37</v>
+      </c>
+      <c r="K198">
+        <f>+IF(E198="","",VLOOKUP(E198,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L198">
+        <f>+IF(E198="","",VLOOKUP(E198,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M198" s="15">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A199" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="B199" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C199" s="17" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D199" t="s">
+        <v>52</v>
+      </c>
+      <c r="E199" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F199" s="6">
+        <f>+VLOOKUP(E199,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G199" s="14">
+        <v>336</v>
+      </c>
+      <c r="H199" s="14">
+        <v>7</v>
+      </c>
+      <c r="I199" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J199" s="12">
+        <v>37</v>
+      </c>
+      <c r="K199">
+        <f>+IF(E199="","",VLOOKUP(E199,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L199">
+        <f>+IF(E199="","",VLOOKUP(E199,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M199" s="15">
+        <v>46278</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A200" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B200" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C200" s="17" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D200" t="s">
+        <v>38</v>
+      </c>
+      <c r="E200" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="F200" s="6">
+        <f>+VLOOKUP(E200,CATALOGO!G:L,6,0)</f>
+        <v>3</v>
+      </c>
+      <c r="G200" s="14">
+        <v>144</v>
+      </c>
+      <c r="H200" s="14">
+        <v>3</v>
+      </c>
+      <c r="I200" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J200" s="12">
+        <v>37</v>
+      </c>
+      <c r="K200">
+        <f>+IF(E200="","",VLOOKUP(E200,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L200">
+        <f>+IF(E200="","",VLOOKUP(E200,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M200" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A201" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B201" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C201" s="17" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D201" t="s">
+        <v>38</v>
+      </c>
+      <c r="E201" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="F201" s="6">
+        <f>+VLOOKUP(E201,CATALOGO!G:L,6,0)</f>
+        <v>6</v>
+      </c>
+      <c r="G201" s="14">
+        <f>16*48</f>
+        <v>768</v>
+      </c>
+      <c r="H201" s="14">
+        <f>24-8</f>
+        <v>16</v>
+      </c>
+      <c r="I201" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J201" s="12">
+        <v>37</v>
+      </c>
+      <c r="K201">
+        <f>+IF(E201="","",VLOOKUP(E201,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L201">
+        <f>+IF(E201="","",VLOOKUP(E201,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M201" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A202" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B202" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C202" s="17" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D202" t="s">
+        <v>38</v>
+      </c>
+      <c r="E202" s="88" t="s">
+        <v>39</v>
+      </c>
+      <c r="F202" s="6">
+        <f>+VLOOKUP(E202,CATALOGO!G:L,6,0)</f>
+        <v>4</v>
+      </c>
+      <c r="G202" s="14">
+        <v>528</v>
+      </c>
+      <c r="H202" s="14">
+        <v>11</v>
+      </c>
+      <c r="I202" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J202" s="12">
+        <v>37</v>
+      </c>
+      <c r="K202">
+        <f>+IF(E202="","",VLOOKUP(E202,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L202">
+        <f>+IF(E202="","",VLOOKUP(E202,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M202" s="15">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A203" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B203" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C203" s="17" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D203" t="s">
+        <v>38</v>
+      </c>
+      <c r="E203" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="F203" s="6">
+        <f>+VLOOKUP(E203,CATALOGO!G:L,6,0)</f>
+        <v>6</v>
+      </c>
+      <c r="G203" s="14">
+        <v>48</v>
+      </c>
+      <c r="H203" s="14">
+        <v>1</v>
+      </c>
+      <c r="I203" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J203" s="12">
+        <v>37</v>
+      </c>
+      <c r="K203">
+        <f>+IF(E203="","",VLOOKUP(E203,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L203">
+        <f>+IF(E203="","",VLOOKUP(E203,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M203" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A204" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B204" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C204" s="17" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D204" t="s">
+        <v>38</v>
+      </c>
+      <c r="E204" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F204" s="6">
+        <f>+VLOOKUP(E204,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G204" s="14">
+        <v>83</v>
+      </c>
+      <c r="H204" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I204" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J204" s="12">
+        <v>37</v>
+      </c>
+      <c r="K204">
+        <f>+IF(E204="","",VLOOKUP(E204,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L204">
+        <f>+IF(E204="","",VLOOKUP(E204,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M204" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A205" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B205" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C205" s="17" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D205" t="s">
+        <v>38</v>
+      </c>
+      <c r="E205" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F205" s="6">
+        <f>+VLOOKUP(E205,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G205" s="14">
+        <v>46</v>
+      </c>
+      <c r="H205" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I205" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J205" s="12">
+        <v>37</v>
+      </c>
+      <c r="K205">
+        <f>+IF(E205="","",VLOOKUP(E205,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L205">
+        <f>+IF(E205="","",VLOOKUP(E205,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M205" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A206" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B206" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C206" s="17" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D206" t="s">
+        <v>38</v>
+      </c>
+      <c r="E206" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F206" s="6">
+        <f>+VLOOKUP(E206,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G206" s="14">
+        <v>34</v>
+      </c>
+      <c r="H206" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I206" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J206" s="12">
+        <v>37</v>
+      </c>
+      <c r="K206">
+        <f>+IF(E206="","",VLOOKUP(E206,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L206">
+        <f>+IF(E206="","",VLOOKUP(E206,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M206" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A207" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B207" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C207" s="17" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D207" t="s">
+        <v>38</v>
+      </c>
+      <c r="E207" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F207" s="6">
+        <f>+VLOOKUP(E207,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G207" s="14">
+        <v>56</v>
+      </c>
+      <c r="H207" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I207" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J207" s="12">
+        <v>37</v>
+      </c>
+      <c r="K207">
+        <f>+IF(E207="","",VLOOKUP(E207,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L207">
+        <f>+IF(E207="","",VLOOKUP(E207,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M207" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A208" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B208" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C208" s="17" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D208" t="s">
+        <v>17</v>
+      </c>
+      <c r="E208" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="F208" s="6">
+        <f>+VLOOKUP(E208,CATALOGO!G:L,6,0)</f>
+        <v>6</v>
+      </c>
+      <c r="G208" s="14">
+        <f>816+240-624</f>
+        <v>432</v>
+      </c>
+      <c r="H208" s="14">
+        <v>9</v>
+      </c>
+      <c r="I208" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J208" s="12">
+        <v>37</v>
+      </c>
+      <c r="K208">
+        <f>+IF(E208="","",VLOOKUP(E208,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L208">
+        <f>+IF(E208="","",VLOOKUP(E208,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M208" s="15">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A209" s="88" t="s">
+        <v>18</v>
+      </c>
+      <c r="B209" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C209" s="17" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D209" t="s">
+        <v>17</v>
+      </c>
+      <c r="E209" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="F209" s="6">
+        <f>+VLOOKUP(E209,CATALOGO!G:L,6,0)</f>
+        <v>6</v>
+      </c>
+      <c r="G209" s="14">
+        <v>288</v>
+      </c>
+      <c r="H209" s="14">
+        <v>6</v>
+      </c>
+      <c r="I209" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J209" s="12">
+        <v>37</v>
+      </c>
+      <c r="K209">
+        <f>+IF(E209="","",VLOOKUP(E209,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L209">
+        <f>+IF(E209="","",VLOOKUP(E209,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M209" s="15">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A210" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B210" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C210" s="17" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D210" t="s">
+        <v>17</v>
+      </c>
+      <c r="E210" s="88" t="s">
+        <v>39</v>
+      </c>
+      <c r="F210" s="6">
+        <f>+VLOOKUP(E210,CATALOGO!G:L,6,0)</f>
+        <v>4</v>
+      </c>
+      <c r="G210" s="14">
+        <v>624</v>
+      </c>
+      <c r="H210" s="14">
+        <v>13</v>
+      </c>
+      <c r="I210" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J210" s="12">
+        <v>37</v>
+      </c>
+      <c r="K210">
+        <f>+IF(E210="","",VLOOKUP(E210,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L210">
+        <f>+IF(E210="","",VLOOKUP(E210,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M210" s="15">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A211" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B211" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C211" s="17" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D211" t="s">
+        <v>17</v>
+      </c>
+      <c r="E211" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F211" s="6">
+        <f>+VLOOKUP(E211,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G211" s="14">
+        <v>1</v>
+      </c>
+      <c r="H211" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I211" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J211" s="12">
+        <v>37</v>
+      </c>
+      <c r="K211">
+        <f>+IF(E211="","",VLOOKUP(E211,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L211">
+        <f>+IF(E211="","",VLOOKUP(E211,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M211" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A212" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B212" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C212" s="17" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D212" t="s">
+        <v>17</v>
+      </c>
+      <c r="E212" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F212" s="6">
+        <f>+VLOOKUP(E212,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G212" s="14">
+        <v>47</v>
+      </c>
+      <c r="H212" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I212" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J212" s="12">
+        <v>37</v>
+      </c>
+      <c r="K212">
+        <f>+IF(E212="","",VLOOKUP(E212,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L212">
+        <f>+IF(E212="","",VLOOKUP(E212,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M212" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A213" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B213" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C213" s="17" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D213" t="s">
+        <v>17</v>
+      </c>
+      <c r="E213" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F213" s="6">
+        <f>+VLOOKUP(E213,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G213" s="14">
+        <v>63</v>
+      </c>
+      <c r="H213" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I213" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J213" s="12">
+        <v>37</v>
+      </c>
+      <c r="K213">
+        <f>+IF(E213="","",VLOOKUP(E213,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L213">
+        <f>+IF(E213="","",VLOOKUP(E213,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M213" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A214" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B214" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C214" s="17" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D214" t="s">
+        <v>17</v>
+      </c>
+      <c r="E214" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F214" s="6">
+        <f>+VLOOKUP(E214,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G214" s="14">
+        <v>26</v>
+      </c>
+      <c r="H214" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I214" s="16">
+        <v>46273</v>
+      </c>
+      <c r="J214" s="12">
+        <v>37</v>
+      </c>
+      <c r="K214">
+        <f>+IF(E214="","",VLOOKUP(E214,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L214">
+        <f>+IF(E214="","",VLOOKUP(E214,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M214" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A215" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B215" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C215" s="17" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D215" t="s">
+        <v>15</v>
+      </c>
+      <c r="E215" s="88" t="s">
+        <v>39</v>
+      </c>
+      <c r="F215" s="6">
+        <f>+VLOOKUP(E215,CATALOGO!G:L,6,0)</f>
+        <v>4</v>
+      </c>
+      <c r="G215" s="14">
+        <v>528</v>
+      </c>
+      <c r="H215" s="14">
+        <f>24-13</f>
+        <v>11</v>
+      </c>
+      <c r="I215" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J215" s="12">
+        <v>37</v>
+      </c>
+      <c r="K215">
+        <f>+IF(E215="","",VLOOKUP(E215,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L215">
+        <f>+IF(E215="","",VLOOKUP(E215,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M215" s="15">
+        <v>46278</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A216" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B216" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C216" s="17" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D216" t="s">
+        <v>40</v>
+      </c>
+      <c r="E216" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F216" s="6">
+        <f>+VLOOKUP(E216,CATALOGO!G:L,6,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G216" s="14">
+        <v>960</v>
+      </c>
+      <c r="H216" s="14">
+        <v>20</v>
+      </c>
+      <c r="I216" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J216" s="12">
+        <v>37</v>
+      </c>
+      <c r="K216">
+        <f>+IF(E216="","",VLOOKUP(E216,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L216">
+        <f>+IF(E216="","",VLOOKUP(E216,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M216" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A217" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="B217" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C217" s="17" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D217" t="s">
+        <v>41</v>
+      </c>
+      <c r="E217" s="88" t="s">
+        <v>44</v>
+      </c>
+      <c r="F217" s="6">
+        <f>+VLOOKUP(E217,CATALOGO!G:L,6,0)</f>
+        <v>1</v>
+      </c>
+      <c r="G217" s="14">
+        <v>288</v>
+      </c>
+      <c r="H217" s="14">
+        <v>6</v>
+      </c>
+      <c r="I217" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J217" s="12">
+        <v>37</v>
+      </c>
+      <c r="K217">
+        <f>+IF(E217="","",VLOOKUP(E217,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L217">
+        <f>+IF(E217="","",VLOOKUP(E217,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M217" s="15">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A218" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="B218" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C218" s="17" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D218" t="s">
+        <v>41</v>
+      </c>
+      <c r="E218" s="88" t="s">
+        <v>44</v>
+      </c>
+      <c r="F218" s="6">
+        <f>+VLOOKUP(E218,CATALOGO!G:L,6,0)</f>
+        <v>1</v>
+      </c>
+      <c r="G218" s="14">
+        <v>1152</v>
+      </c>
+      <c r="H218" s="14">
+        <v>24</v>
+      </c>
+      <c r="I218" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J218" s="12">
+        <v>37</v>
+      </c>
+      <c r="K218">
+        <f>+IF(E218="","",VLOOKUP(E218,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L218">
+        <f>+IF(E218="","",VLOOKUP(E218,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M218" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A219" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B219" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C219" s="17" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D219" t="s">
+        <v>17</v>
+      </c>
+      <c r="E219" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="F219" s="6">
+        <f>+VLOOKUP(E219,CATALOGO!G:L,6,0)</f>
+        <v>6</v>
+      </c>
+      <c r="G219" s="14">
+        <v>336</v>
+      </c>
+      <c r="H219" s="14">
+        <v>7</v>
+      </c>
+      <c r="I219" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J219" s="12">
+        <v>37</v>
+      </c>
+      <c r="K219">
+        <f>+IF(E219="","",VLOOKUP(E219,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L219">
+        <f>+IF(E219="","",VLOOKUP(E219,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M219" s="15">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A220" s="88" t="s">
+        <v>18</v>
+      </c>
+      <c r="B220" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C220" s="17" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D220" t="s">
+        <v>17</v>
+      </c>
+      <c r="E220" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="F220" s="6">
+        <f>+VLOOKUP(E220,CATALOGO!G:L,6,0)</f>
+        <v>3</v>
+      </c>
+      <c r="G220" s="14">
+        <v>96</v>
+      </c>
+      <c r="H220" s="14">
+        <v>2</v>
+      </c>
+      <c r="I220" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J220" s="12">
+        <v>37</v>
+      </c>
+      <c r="K220">
+        <f>+IF(E220="","",VLOOKUP(E220,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L220">
+        <f>+IF(E220="","",VLOOKUP(E220,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M220" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A221" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B221" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C221" s="17" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D221" t="s">
+        <v>17</v>
+      </c>
+      <c r="E221" s="88" t="s">
+        <v>39</v>
+      </c>
+      <c r="F221" s="6">
+        <f>+VLOOKUP(E221,CATALOGO!G:L,6,0)</f>
+        <v>4</v>
+      </c>
+      <c r="G221" s="14">
+        <f>1104-336</f>
+        <v>768</v>
+      </c>
+      <c r="H221" s="14">
+        <v>16</v>
+      </c>
+      <c r="I221" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J221" s="12">
+        <v>37</v>
+      </c>
+      <c r="K221">
+        <f>+IF(E221="","",VLOOKUP(E221,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L221">
+        <f>+IF(E221="","",VLOOKUP(E221,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M221" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A222" s="88" t="s">
+        <v>18</v>
+      </c>
+      <c r="B222" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C222" s="17" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D222" t="s">
+        <v>17</v>
+      </c>
+      <c r="E222" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="F222" s="6">
+        <f>+VLOOKUP(E222,CATALOGO!G:L,6,0)</f>
+        <v>6</v>
+      </c>
+      <c r="G222" s="14">
+        <v>144</v>
+      </c>
+      <c r="H222" s="14">
+        <v>3</v>
+      </c>
+      <c r="I222" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J222" s="12">
+        <v>37</v>
+      </c>
+      <c r="K222">
+        <f>+IF(E222="","",VLOOKUP(E222,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L222">
+        <f>+IF(E222="","",VLOOKUP(E222,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M222" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A223" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B223" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C223" s="17" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D223" t="s">
+        <v>17</v>
+      </c>
+      <c r="E223" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F223" s="6">
+        <f>+VLOOKUP(E223,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G223" s="14">
+        <v>0</v>
+      </c>
+      <c r="H223" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I223" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J223" s="12">
+        <v>37</v>
+      </c>
+      <c r="K223">
+        <f>+IF(E223="","",VLOOKUP(E223,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L223">
+        <f>+IF(E223="","",VLOOKUP(E223,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M223" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A224" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B224" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C224" s="17" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D224" t="s">
+        <v>17</v>
+      </c>
+      <c r="E224" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F224" s="6">
+        <f>+VLOOKUP(E224,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G224" s="14">
+        <v>53</v>
+      </c>
+      <c r="H224" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I224" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J224" s="12">
+        <v>37</v>
+      </c>
+      <c r="K224">
+        <f>+IF(E224="","",VLOOKUP(E224,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L224">
+        <f>+IF(E224="","",VLOOKUP(E224,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M224" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A225" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B225" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C225" s="17" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D225" t="s">
+        <v>17</v>
+      </c>
+      <c r="E225" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F225" s="6">
+        <f>+VLOOKUP(E225,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G225" s="14">
+        <v>54</v>
+      </c>
+      <c r="H225" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I225" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J225" s="12">
+        <v>37</v>
+      </c>
+      <c r="K225">
+        <f>+IF(E225="","",VLOOKUP(E225,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L225">
+        <f>+IF(E225="","",VLOOKUP(E225,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M225" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A226" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B226" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C226" s="17" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D226" t="s">
+        <v>17</v>
+      </c>
+      <c r="E226" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F226" s="6">
+        <f>+VLOOKUP(E226,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G226" s="14">
+        <v>20</v>
+      </c>
+      <c r="H226" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I226" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J226" s="12">
+        <v>37</v>
+      </c>
+      <c r="K226">
+        <f>+IF(E226="","",VLOOKUP(E226,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L226">
+        <f>+IF(E226="","",VLOOKUP(E226,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M226" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A227" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B227" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C227" s="17" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D227" t="s">
+        <v>53</v>
+      </c>
+      <c r="E227" s="88" t="s">
+        <v>39</v>
+      </c>
+      <c r="F227" s="6">
+        <f>+VLOOKUP(E227,CATALOGO!G:L,6,0)</f>
+        <v>4</v>
+      </c>
+      <c r="G227" s="14">
+        <v>336</v>
+      </c>
+      <c r="H227" s="14">
+        <v>7</v>
+      </c>
+      <c r="I227" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J227" s="12">
+        <v>37</v>
+      </c>
+      <c r="K227">
+        <f>+IF(E227="","",VLOOKUP(E227,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L227">
+        <f>+IF(E227="","",VLOOKUP(E227,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M227" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A228" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B228" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C228" s="17" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D228" t="s">
+        <v>53</v>
+      </c>
+      <c r="E228" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="F228" s="6">
+        <f>+VLOOKUP(E228,CATALOGO!G:L,6,0)</f>
+        <v>6</v>
+      </c>
+      <c r="G228" s="14">
+        <v>864</v>
+      </c>
+      <c r="H228" s="14">
+        <v>18</v>
+      </c>
+      <c r="I228" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J228" s="12">
+        <v>37</v>
+      </c>
+      <c r="K228">
+        <f>+IF(E228="","",VLOOKUP(E228,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L228">
+        <f>+IF(E228="","",VLOOKUP(E228,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M228" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A229" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B229" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C229" s="17" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D229" t="s">
+        <v>53</v>
+      </c>
+      <c r="E229" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F229" s="6">
+        <f>+VLOOKUP(E229,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G229" s="14">
+        <v>21</v>
+      </c>
+      <c r="H229" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I229" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J229" s="12">
+        <v>37</v>
+      </c>
+      <c r="K229">
+        <f>+IF(E229="","",VLOOKUP(E229,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L229">
+        <f>+IF(E229="","",VLOOKUP(E229,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M229" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A230" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B230" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C230" s="17" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D230" t="s">
+        <v>53</v>
+      </c>
+      <c r="E230" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F230" s="6">
+        <f>+VLOOKUP(E230,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G230" s="14">
+        <v>22</v>
+      </c>
+      <c r="H230" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I230" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J230" s="12">
+        <v>37</v>
+      </c>
+      <c r="K230">
+        <f>+IF(E230="","",VLOOKUP(E230,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L230">
+        <f>+IF(E230="","",VLOOKUP(E230,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M230" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A231" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B231" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C231" s="17" t="s">
+        <v>1476</v>
+      </c>
+      <c r="D231" t="s">
+        <v>53</v>
+      </c>
+      <c r="E231" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F231" s="6">
+        <f>+VLOOKUP(E231,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G231" s="14">
+        <v>20</v>
+      </c>
+      <c r="H231" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I231" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J231" s="12">
+        <v>37</v>
+      </c>
+      <c r="K231">
+        <f>+IF(E231="","",VLOOKUP(E231,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L231">
+        <f>+IF(E231="","",VLOOKUP(E231,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M231" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A232" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B232" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C232" s="17" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D232" t="s">
+        <v>53</v>
+      </c>
+      <c r="E232" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F232" s="6">
+        <f>+VLOOKUP(E232,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G232" s="14">
+        <v>45</v>
+      </c>
+      <c r="H232" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I232" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J232" s="12">
+        <v>37</v>
+      </c>
+      <c r="K232">
+        <f>+IF(E232="","",VLOOKUP(E232,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L232">
+        <f>+IF(E232="","",VLOOKUP(E232,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M232" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A233" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B233" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C233" s="17" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D233" t="s">
+        <v>37</v>
+      </c>
+      <c r="E233" s="88" t="s">
+        <v>23</v>
+      </c>
+      <c r="F233" s="6">
+        <f>+VLOOKUP(E233,CATALOGO!G:L,6,0)</f>
+        <v>5</v>
+      </c>
+      <c r="G233" s="14">
+        <v>1104</v>
+      </c>
+      <c r="H233" s="14">
+        <v>23</v>
+      </c>
+      <c r="I233" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J233" s="12">
+        <v>37</v>
+      </c>
+      <c r="K233">
+        <f>+IF(E233="","",VLOOKUP(E233,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L233">
+        <f>+IF(E233="","",VLOOKUP(E233,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M233" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A234" s="88" t="s">
+        <v>21</v>
+      </c>
+      <c r="B234" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C234" s="17" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D234" t="s">
+        <v>37</v>
+      </c>
+      <c r="E234" s="88" t="s">
+        <v>23</v>
+      </c>
+      <c r="F234" s="6">
+        <f>+VLOOKUP(E234,CATALOGO!G:L,6,0)</f>
+        <v>5</v>
+      </c>
+      <c r="G234" s="14">
+        <v>48</v>
+      </c>
+      <c r="H234" s="14">
+        <v>1</v>
+      </c>
+      <c r="I234" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J234" s="12">
+        <v>37</v>
+      </c>
+      <c r="K234">
+        <f>+IF(E234="","",VLOOKUP(E234,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L234">
+        <f>+IF(E234="","",VLOOKUP(E234,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M234" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A235" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B235" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C235" s="17" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D235" t="s">
+        <v>37</v>
+      </c>
+      <c r="E235" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F235" s="6">
+        <f>+VLOOKUP(E235,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G235" s="14">
+        <v>81</v>
+      </c>
+      <c r="H235" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I235" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J235" s="12">
+        <v>37</v>
+      </c>
+      <c r="K235">
+        <f>+IF(E235="","",VLOOKUP(E235,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L235">
+        <f>+IF(E235="","",VLOOKUP(E235,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M235" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A236" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B236" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C236" s="17" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D236" t="s">
+        <v>37</v>
+      </c>
+      <c r="E236" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F236" s="6">
+        <f>+VLOOKUP(E236,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G236" s="14">
+        <v>53</v>
+      </c>
+      <c r="H236" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I236" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J236" s="12">
+        <v>37</v>
+      </c>
+      <c r="K236">
+        <f>+IF(E236="","",VLOOKUP(E236,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L236">
+        <f>+IF(E236="","",VLOOKUP(E236,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M236" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A237" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B237" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C237" s="17" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D237" t="s">
+        <v>37</v>
+      </c>
+      <c r="E237" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F237" s="6">
+        <f>+VLOOKUP(E237,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G237" s="14">
+        <v>14</v>
+      </c>
+      <c r="H237" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I237" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J237" s="12">
+        <v>37</v>
+      </c>
+      <c r="K237">
+        <f>+IF(E237="","",VLOOKUP(E237,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L237">
+        <f>+IF(E237="","",VLOOKUP(E237,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M237" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A238" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B238" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C238" s="17" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D238" t="s">
+        <v>37</v>
+      </c>
+      <c r="E238" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F238" s="6">
+        <f>+VLOOKUP(E238,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G238" s="14">
+        <v>48</v>
+      </c>
+      <c r="H238" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I238" s="16">
+        <v>46274</v>
+      </c>
+      <c r="J238" s="12">
+        <v>37</v>
+      </c>
+      <c r="K238">
+        <f>+IF(E238="","",VLOOKUP(E238,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L238">
+        <f>+IF(E238="","",VLOOKUP(E238,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M238" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A239" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B239" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C239" s="17" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D239" t="s">
+        <v>40</v>
+      </c>
+      <c r="E239" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F239" s="6">
+        <f>+VLOOKUP(E239,CATALOGO!G:L,6,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G239" s="14">
+        <v>960</v>
+      </c>
+      <c r="H239" s="14">
+        <v>20</v>
+      </c>
+      <c r="I239" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J239" s="12">
+        <v>37</v>
+      </c>
+      <c r="K239">
+        <f>+IF(E239="","",VLOOKUP(E239,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L239">
+        <f>+IF(E239="","",VLOOKUP(E239,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M239" s="15">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A240" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B240" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C240" s="17" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D240" t="s">
+        <v>41</v>
+      </c>
+      <c r="E240" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F240" s="6">
+        <f>+VLOOKUP(E240,CATALOGO!G:L,6,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G240" s="14">
+        <v>960</v>
+      </c>
+      <c r="H240" s="14">
+        <v>20</v>
+      </c>
+      <c r="I240" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J240" s="12">
+        <v>37</v>
+      </c>
+      <c r="K240">
+        <f>+IF(E240="","",VLOOKUP(E240,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L240">
+        <f>+IF(E240="","",VLOOKUP(E240,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M240" s="15">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A241" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B241" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C241" s="17" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D241" t="s">
+        <v>54</v>
+      </c>
+      <c r="E241" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="F241" s="6">
+        <f>+VLOOKUP(E241,CATALOGO!G:L,6,0)</f>
+        <v>3</v>
+      </c>
+      <c r="G241" s="14">
+        <v>1056</v>
+      </c>
+      <c r="H241" s="14">
+        <v>22</v>
+      </c>
+      <c r="I241" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J241" s="12">
+        <v>37</v>
+      </c>
+      <c r="K241">
+        <f>+IF(E241="","",VLOOKUP(E241,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L241">
+        <f>+IF(E241="","",VLOOKUP(E241,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M241" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A242" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B242" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C242" s="17" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D242" t="s">
+        <v>55</v>
+      </c>
+      <c r="E242" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F242" s="6">
+        <f>+VLOOKUP(E242,CATALOGO!G:L,6,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G242" s="14">
+        <v>480</v>
+      </c>
+      <c r="H242" s="14">
+        <v>10</v>
+      </c>
+      <c r="I242" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J242" s="12">
+        <v>37</v>
+      </c>
+      <c r="K242">
+        <f>+IF(E242="","",VLOOKUP(E242,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L242">
+        <f>+IF(E242="","",VLOOKUP(E242,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M242" s="15">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A243" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="B243" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C243" s="17" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D243" t="s">
+        <v>38</v>
+      </c>
+      <c r="E243" s="88" t="s">
+        <v>44</v>
+      </c>
+      <c r="F243" s="6">
+        <f>+VLOOKUP(E243,CATALOGO!G:L,6,0)</f>
+        <v>1</v>
+      </c>
+      <c r="G243" s="14">
+        <f>4*48</f>
+        <v>192</v>
+      </c>
+      <c r="H243" s="14">
+        <v>4</v>
+      </c>
+      <c r="I243" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J243" s="12">
+        <v>37</v>
+      </c>
+      <c r="K243">
+        <f>+IF(E243="","",VLOOKUP(E243,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L243">
+        <f>+IF(E243="","",VLOOKUP(E243,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M243" s="15">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A244" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="B244" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C244" s="17" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D244" t="s">
+        <v>38</v>
+      </c>
+      <c r="E244" s="88" t="s">
+        <v>44</v>
+      </c>
+      <c r="F244" s="6">
+        <f>+VLOOKUP(E244,CATALOGO!G:L,6,0)</f>
+        <v>1</v>
+      </c>
+      <c r="G244" s="14">
+        <v>960</v>
+      </c>
+      <c r="H244" s="14">
+        <v>20</v>
+      </c>
+      <c r="I244" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J244" s="12">
+        <v>37</v>
+      </c>
+      <c r="K244">
+        <f>+IF(E244="","",VLOOKUP(E244,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L244">
+        <f>+IF(E244="","",VLOOKUP(E244,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M244" s="15">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A245" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B245" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C245" s="17" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D245" t="s">
+        <v>38</v>
+      </c>
+      <c r="E245" s="88" t="s">
+        <v>56</v>
+      </c>
+      <c r="F245" s="6">
+        <f>+VLOOKUP(E245,CATALOGO!G:L,6,0)</f>
+        <v>2</v>
+      </c>
+      <c r="G245" s="14">
+        <v>480</v>
+      </c>
+      <c r="H245" s="14">
+        <v>10</v>
+      </c>
+      <c r="I245" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J245" s="12">
+        <v>37</v>
+      </c>
+      <c r="K245">
+        <f>+IF(E245="","",VLOOKUP(E245,CATALOGO!G:I,2,0))</f>
+        <v>2.5</v>
+      </c>
+      <c r="L245">
+        <f>+IF(E245="","",VLOOKUP(E245,CATALOGO!G:I,3,0))</f>
+        <v>60</v>
+      </c>
+      <c r="M245" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A246" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B246" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C246" s="17" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D246" t="s">
+        <v>38</v>
+      </c>
+      <c r="E246" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F246" s="6">
+        <f>+VLOOKUP(E246,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G246" s="14">
+        <v>1</v>
+      </c>
+      <c r="H246" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I246" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J246" s="12">
+        <v>37</v>
+      </c>
+      <c r="K246">
+        <f>+IF(E246="","",VLOOKUP(E246,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L246">
+        <f>+IF(E246="","",VLOOKUP(E246,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M246" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A247" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B247" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C247" s="17" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D247" t="s">
+        <v>38</v>
+      </c>
+      <c r="E247" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F247" s="6">
+        <f>+VLOOKUP(E247,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G247" s="14">
+        <v>38</v>
+      </c>
+      <c r="H247" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I247" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J247" s="12">
+        <v>37</v>
+      </c>
+      <c r="K247">
+        <f>+IF(E247="","",VLOOKUP(E247,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L247">
+        <f>+IF(E247="","",VLOOKUP(E247,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M247" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A248" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B248" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C248" s="17" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D248" t="s">
+        <v>38</v>
+      </c>
+      <c r="E248" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F248" s="6">
+        <f>+VLOOKUP(E248,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G248" s="14">
+        <v>18</v>
+      </c>
+      <c r="H248" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I248" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J248" s="12">
+        <v>37</v>
+      </c>
+      <c r="K248">
+        <f>+IF(E248="","",VLOOKUP(E248,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L248">
+        <f>+IF(E248="","",VLOOKUP(E248,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M248" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A249" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B249" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C249" s="17" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D249" t="s">
+        <v>38</v>
+      </c>
+      <c r="E249" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F249" s="6">
+        <f>+VLOOKUP(E249,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G249" s="14">
+        <v>72</v>
+      </c>
+      <c r="H249" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I249" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J249" s="12">
+        <v>37</v>
+      </c>
+      <c r="K249">
+        <f>+IF(E249="","",VLOOKUP(E249,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L249">
+        <f>+IF(E249="","",VLOOKUP(E249,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M249" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A250" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B250" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C250" s="17" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D250" t="s">
+        <v>37</v>
+      </c>
+      <c r="E250" s="88" t="s">
+        <v>23</v>
+      </c>
+      <c r="F250" s="6">
+        <f>+VLOOKUP(E250,CATALOGO!G:L,6,0)</f>
+        <v>5</v>
+      </c>
+      <c r="G250" s="14">
+        <v>1104</v>
+      </c>
+      <c r="H250" s="14">
+        <v>23</v>
+      </c>
+      <c r="I250" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J250" s="12">
+        <v>37</v>
+      </c>
+      <c r="K250">
+        <f>+IF(E250="","",VLOOKUP(E250,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L250">
+        <f>+IF(E250="","",VLOOKUP(E250,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M250" s="15">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A251" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B251" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C251" s="17" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D251" t="s">
+        <v>37</v>
+      </c>
+      <c r="E251" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F251" s="6">
+        <f>+VLOOKUP(E251,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G251" s="14">
+        <v>1</v>
+      </c>
+      <c r="H251" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I251" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J251" s="12">
+        <v>37</v>
+      </c>
+      <c r="K251">
+        <f>+IF(E251="","",VLOOKUP(E251,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L251">
+        <f>+IF(E251="","",VLOOKUP(E251,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M251" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A252" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B252" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C252" s="17" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D252" t="s">
+        <v>37</v>
+      </c>
+      <c r="E252" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F252" s="6">
+        <f>+VLOOKUP(E252,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G252" s="14">
+        <v>83</v>
+      </c>
+      <c r="H252" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I252" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J252" s="12">
+        <v>37</v>
+      </c>
+      <c r="K252">
+        <f>+IF(E252="","",VLOOKUP(E252,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L252">
+        <f>+IF(E252="","",VLOOKUP(E252,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M252" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A253" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B253" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C253" s="17" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D253" t="s">
+        <v>37</v>
+      </c>
+      <c r="E253" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F253" s="6">
+        <f>+VLOOKUP(E253,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G253" s="14">
+        <v>20</v>
+      </c>
+      <c r="H253" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I253" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J253" s="12">
+        <v>37</v>
+      </c>
+      <c r="K253">
+        <f>+IF(E253="","",VLOOKUP(E253,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L253">
+        <f>+IF(E253="","",VLOOKUP(E253,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M253" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A254" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B254" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C254" s="17" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D254" t="s">
+        <v>37</v>
+      </c>
+      <c r="E254" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F254" s="6">
+        <f>+VLOOKUP(E254,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G254" s="14">
+        <v>50</v>
+      </c>
+      <c r="H254" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I254" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J254" s="12">
+        <v>37</v>
+      </c>
+      <c r="K254">
+        <f>+IF(E254="","",VLOOKUP(E254,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L254">
+        <f>+IF(E254="","",VLOOKUP(E254,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M254" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A255" s="88" t="s">
+        <v>21</v>
+      </c>
+      <c r="B255" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C255" s="17" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D255" t="s">
+        <v>17</v>
+      </c>
+      <c r="E255" s="88" t="s">
+        <v>23</v>
+      </c>
+      <c r="F255" s="6">
+        <f>+VLOOKUP(E255,CATALOGO!G:L,6,0)</f>
+        <v>5</v>
+      </c>
+      <c r="G255" s="14">
+        <v>48</v>
+      </c>
+      <c r="H255" s="14">
+        <v>1</v>
+      </c>
+      <c r="I255" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J255" s="12">
+        <v>37</v>
+      </c>
+      <c r="K255">
+        <f>+IF(E255="","",VLOOKUP(E255,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L255">
+        <f>+IF(E255="","",VLOOKUP(E255,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M255" s="15">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A256" s="88" t="s">
+        <v>18</v>
+      </c>
+      <c r="B256" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C256" s="17" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D256" t="s">
+        <v>17</v>
+      </c>
+      <c r="E256" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="F256" s="6">
+        <f>+VLOOKUP(E256,CATALOGO!G:L,6,0)</f>
+        <v>6</v>
+      </c>
+      <c r="G256" s="14">
+        <v>144</v>
+      </c>
+      <c r="H256" s="14">
+        <v>3</v>
+      </c>
+      <c r="I256" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J256" s="12">
+        <v>37</v>
+      </c>
+      <c r="K256">
+        <f>+IF(E256="","",VLOOKUP(E256,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L256">
+        <f>+IF(E256="","",VLOOKUP(E256,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M256" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A257" s="88" t="s">
+        <v>21</v>
+      </c>
+      <c r="B257" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C257" s="17" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D257" t="s">
+        <v>17</v>
+      </c>
+      <c r="E257" s="88" t="s">
+        <v>56</v>
+      </c>
+      <c r="F257" s="6">
+        <f>+VLOOKUP(E257,CATALOGO!G:L,6,0)</f>
+        <v>2</v>
+      </c>
+      <c r="G257" s="14">
+        <v>5</v>
+      </c>
+      <c r="H257" s="14">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="I257" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J257" s="12">
+        <v>37</v>
+      </c>
+      <c r="K257">
+        <f>+IF(E257="","",VLOOKUP(E257,CATALOGO!G:I,2,0))</f>
+        <v>2.5</v>
+      </c>
+      <c r="L257">
+        <f>+IF(E257="","",VLOOKUP(E257,CATALOGO!G:I,3,0))</f>
+        <v>60</v>
+      </c>
+      <c r="M257" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A258" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="B258" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C258" s="17" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D258" t="s">
+        <v>17</v>
+      </c>
+      <c r="E258" s="88" t="s">
+        <v>44</v>
+      </c>
+      <c r="F258" s="6">
+        <f>+VLOOKUP(E258,CATALOGO!G:L,6,0)</f>
+        <v>1</v>
+      </c>
+      <c r="G258" s="14">
+        <f>10*48</f>
+        <v>480</v>
+      </c>
+      <c r="H258" s="14">
+        <v>10</v>
+      </c>
+      <c r="I258" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J258" s="12">
+        <v>37</v>
+      </c>
+      <c r="K258">
+        <f>+IF(E258="","",VLOOKUP(E258,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L258">
+        <f>+IF(E258="","",VLOOKUP(E258,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M258" s="15">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A259" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B259" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C259" s="17" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D259" t="s">
+        <v>17</v>
+      </c>
+      <c r="E259" s="88" t="s">
+        <v>56</v>
+      </c>
+      <c r="F259" s="6">
+        <f>+VLOOKUP(E259,CATALOGO!G:L,6,0)</f>
+        <v>2</v>
+      </c>
+      <c r="G259" s="14">
+        <f>12*48</f>
+        <v>576</v>
+      </c>
+      <c r="H259" s="14">
+        <v>12</v>
+      </c>
+      <c r="I259" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J259" s="12">
+        <v>37</v>
+      </c>
+      <c r="K259">
+        <f>+IF(E259="","",VLOOKUP(E259,CATALOGO!G:I,2,0))</f>
+        <v>2.5</v>
+      </c>
+      <c r="L259">
+        <f>+IF(E259="","",VLOOKUP(E259,CATALOGO!G:I,3,0))</f>
+        <v>60</v>
+      </c>
+      <c r="M259" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A260" s="88" t="s">
+        <v>18</v>
+      </c>
+      <c r="B260" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C260" s="17" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D260" t="s">
+        <v>17</v>
+      </c>
+      <c r="E260" s="88" t="s">
+        <v>56</v>
+      </c>
+      <c r="F260" s="6">
+        <f>+VLOOKUP(E260,CATALOGO!G:L,6,0)</f>
+        <v>2</v>
+      </c>
+      <c r="G260" s="14">
+        <v>96</v>
+      </c>
+      <c r="H260" s="14">
+        <v>2</v>
+      </c>
+      <c r="I260" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J260" s="12">
+        <v>37</v>
+      </c>
+      <c r="K260">
+        <f>+IF(E260="","",VLOOKUP(E260,CATALOGO!G:I,2,0))</f>
+        <v>2.5</v>
+      </c>
+      <c r="L260">
+        <f>+IF(E260="","",VLOOKUP(E260,CATALOGO!G:I,3,0))</f>
+        <v>60</v>
+      </c>
+      <c r="M260" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A261" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B261" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C261" s="17" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D261" t="s">
+        <v>17</v>
+      </c>
+      <c r="E261" s="88" t="s">
+        <v>39</v>
+      </c>
+      <c r="F261" s="6">
+        <f>+VLOOKUP(E261,CATALOGO!G:L,6,0)</f>
+        <v>4</v>
+      </c>
+      <c r="G261" s="14">
+        <v>48</v>
+      </c>
+      <c r="H261" s="14">
+        <v>1</v>
+      </c>
+      <c r="I261" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J261" s="12">
+        <v>37</v>
+      </c>
+      <c r="K261">
+        <f>+IF(E261="","",VLOOKUP(E261,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L261">
+        <f>+IF(E261="","",VLOOKUP(E261,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M261" s="15">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A262" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B262" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C262" s="17" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D262" t="s">
+        <v>17</v>
+      </c>
+      <c r="E262" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F262" s="6">
+        <f>+VLOOKUP(E262,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G262" s="14">
+        <v>1</v>
+      </c>
+      <c r="H262" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I262" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J262" s="12">
+        <v>37</v>
+      </c>
+      <c r="K262">
+        <f>+IF(E262="","",VLOOKUP(E262,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L262">
+        <f>+IF(E262="","",VLOOKUP(E262,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M262" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A263" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B263" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C263" s="17" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D263" t="s">
+        <v>17</v>
+      </c>
+      <c r="E263" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F263" s="6">
+        <f>+VLOOKUP(E263,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G263" s="14">
+        <v>52</v>
+      </c>
+      <c r="H263" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I263" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J263" s="12">
+        <v>37</v>
+      </c>
+      <c r="K263">
+        <f>+IF(E263="","",VLOOKUP(E263,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L263">
+        <f>+IF(E263="","",VLOOKUP(E263,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M263" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A264" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B264" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C264" s="17" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D264" t="s">
+        <v>17</v>
+      </c>
+      <c r="E264" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F264" s="6">
+        <f>+VLOOKUP(E264,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G264" s="14">
+        <v>76</v>
+      </c>
+      <c r="H264" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I264" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J264" s="12">
+        <v>37</v>
+      </c>
+      <c r="K264">
+        <f>+IF(E264="","",VLOOKUP(E264,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L264">
+        <f>+IF(E264="","",VLOOKUP(E264,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M264" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A265" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B265" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C265" s="17" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D265" t="s">
+        <v>17</v>
+      </c>
+      <c r="E265" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F265" s="6">
+        <f>+VLOOKUP(E265,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G265" s="14">
+        <v>24</v>
+      </c>
+      <c r="H265" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I265" s="16">
+        <v>46275</v>
+      </c>
+      <c r="J265" s="12">
+        <v>37</v>
+      </c>
+      <c r="K265">
+        <f>+IF(E265="","",VLOOKUP(E265,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L265">
+        <f>+IF(E265="","",VLOOKUP(E265,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M265" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A266" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B266" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C266" s="17" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D266" t="s">
+        <v>40</v>
+      </c>
+      <c r="E266" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F266" s="6">
+        <f>+VLOOKUP(E266,CATALOGO!G:L,6,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G266" s="14">
+        <v>960</v>
+      </c>
+      <c r="H266" s="14">
+        <v>20</v>
+      </c>
+      <c r="I266" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J266" s="12">
+        <v>37</v>
+      </c>
+      <c r="K266">
+        <f>+IF(E266="","",VLOOKUP(E266,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L266">
+        <f>+IF(E266="","",VLOOKUP(E266,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M266" s="15">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A267" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B267" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C267" s="17" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D267" t="s">
+        <v>55</v>
+      </c>
+      <c r="E267" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F267" s="6">
+        <f>+VLOOKUP(E267,CATALOGO!G:L,6,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G267" s="14">
+        <v>480</v>
+      </c>
+      <c r="H267" s="14">
+        <v>10</v>
+      </c>
+      <c r="I267" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J267" s="12">
+        <v>37</v>
+      </c>
+      <c r="K267">
+        <f>+IF(E267="","",VLOOKUP(E267,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L267">
+        <f>+IF(E267="","",VLOOKUP(E267,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M267" s="15">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A268" s="88" t="s">
+        <v>57</v>
+      </c>
+      <c r="B268" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C268" s="17" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D268" t="s">
+        <v>59</v>
+      </c>
+      <c r="E268" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F268" s="6">
+        <f>+VLOOKUP(E268,CATALOGO!G:L,6,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G268" s="14">
+        <v>1008</v>
+      </c>
+      <c r="H268" s="14">
+        <v>24</v>
+      </c>
+      <c r="I268" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J268" s="12">
+        <v>37</v>
+      </c>
+      <c r="K268">
+        <f>+IF(E268="","",VLOOKUP(E268,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L268">
+        <f>+IF(E268="","",VLOOKUP(E268,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M268" s="15">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A269" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="B269" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C269" s="17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E269" s="88" t="s">
+        <v>44</v>
+      </c>
+      <c r="F269" s="6">
+        <f>+VLOOKUP(E269,CATALOGO!G:L,6,0)</f>
+        <v>1</v>
+      </c>
+      <c r="G269" s="14">
+        <v>480</v>
+      </c>
+      <c r="H269" s="14">
+        <v>10</v>
+      </c>
+      <c r="I269" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J269" s="12">
+        <v>37</v>
+      </c>
+      <c r="K269">
+        <f>+IF(E269="","",VLOOKUP(E269,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L269">
+        <f>+IF(E269="","",VLOOKUP(E269,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M269" s="15">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A270" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B270" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C270" s="17" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D270" t="s">
+        <v>38</v>
+      </c>
+      <c r="E270" s="88" t="s">
+        <v>39</v>
+      </c>
+      <c r="F270" s="6">
+        <f>+VLOOKUP(E270,CATALOGO!G:L,6,0)</f>
+        <v>4</v>
+      </c>
+      <c r="G270" s="14">
+        <v>720</v>
+      </c>
+      <c r="H270" s="14">
+        <v>15</v>
+      </c>
+      <c r="I270" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J270" s="12">
+        <v>37</v>
+      </c>
+      <c r="K270">
+        <f>+IF(E270="","",VLOOKUP(E270,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L270">
+        <f>+IF(E270="","",VLOOKUP(E270,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M270" s="15">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A271" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B271" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C271" s="17" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D271" t="s">
+        <v>17</v>
+      </c>
+      <c r="E271" s="88" t="s">
+        <v>39</v>
+      </c>
+      <c r="F271" s="6">
+        <f>+VLOOKUP(E271,CATALOGO!G:L,6,0)</f>
+        <v>4</v>
+      </c>
+      <c r="G271" s="14">
+        <v>240</v>
+      </c>
+      <c r="H271" s="14">
+        <v>5</v>
+      </c>
+      <c r="I271" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J271" s="12">
+        <v>37</v>
+      </c>
+      <c r="K271">
+        <f>+IF(E271="","",VLOOKUP(E271,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L271">
+        <f>+IF(E271="","",VLOOKUP(E271,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M271" s="15">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A272" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B272" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C272" s="17" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D272" t="s">
+        <v>37</v>
+      </c>
+      <c r="E272" s="88" t="s">
+        <v>39</v>
+      </c>
+      <c r="F272" s="6">
+        <f>+VLOOKUP(E272,CATALOGO!G:L,6,0)</f>
+        <v>4</v>
+      </c>
+      <c r="G272" s="14">
+        <v>192</v>
+      </c>
+      <c r="H272" s="14">
+        <v>4</v>
+      </c>
+      <c r="I272" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J272" s="12">
+        <v>37</v>
+      </c>
+      <c r="K272">
+        <f>+IF(E272="","",VLOOKUP(E272,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L272">
+        <f>+IF(E272="","",VLOOKUP(E272,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M272" s="15">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A273" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B273" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C273" s="17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E273" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F273" s="6">
+        <f>+VLOOKUP(E273,CATALOGO!G:L,6,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G273" s="14">
+        <v>960</v>
+      </c>
+      <c r="H273" s="14">
+        <v>20</v>
+      </c>
+      <c r="I273" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J273" s="12">
+        <v>37</v>
+      </c>
+      <c r="K273">
+        <f>+IF(E273="","",VLOOKUP(E273,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L273">
+        <f>+IF(E273="","",VLOOKUP(E273,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M273" s="15">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A274" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="B274" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C274" s="17" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D274" t="s">
+        <v>38</v>
+      </c>
+      <c r="E274" s="88" t="s">
+        <v>44</v>
+      </c>
+      <c r="F274" s="6">
+        <f>+VLOOKUP(E274,CATALOGO!G:L,6,0)</f>
+        <v>1</v>
+      </c>
+      <c r="G274" s="14">
+        <v>960</v>
+      </c>
+      <c r="H274" s="14">
+        <v>20</v>
+      </c>
+      <c r="I274" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J274" s="12">
+        <v>37</v>
+      </c>
+      <c r="K274">
+        <f>+IF(E274="","",VLOOKUP(E274,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L274">
+        <f>+IF(E274="","",VLOOKUP(E274,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M274" s="15">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A275" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B275" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C275" s="17" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D275" t="s">
+        <v>38</v>
+      </c>
+      <c r="E275" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F275" s="6">
+        <f>+VLOOKUP(E275,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G275" s="14">
+        <v>1</v>
+      </c>
+      <c r="H275" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I275" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J275" s="12">
+        <v>37</v>
+      </c>
+      <c r="K275">
+        <f>+IF(E275="","",VLOOKUP(E275,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L275">
+        <f>+IF(E275="","",VLOOKUP(E275,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M275" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A276" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B276" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C276" s="17" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D276" t="s">
+        <v>38</v>
+      </c>
+      <c r="E276" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F276" s="6">
+        <f>+VLOOKUP(E276,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G276" s="14">
+        <v>38</v>
+      </c>
+      <c r="H276" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I276" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J276" s="12">
+        <v>37</v>
+      </c>
+      <c r="K276">
+        <f>+IF(E276="","",VLOOKUP(E276,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L276">
+        <f>+IF(E276="","",VLOOKUP(E276,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M276" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A277" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B277" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C277" s="17" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D277" t="s">
+        <v>38</v>
+      </c>
+      <c r="E277" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F277" s="6">
+        <f>+VLOOKUP(E277,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G277" s="14">
+        <v>18</v>
+      </c>
+      <c r="H277" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I277" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J277" s="12">
+        <v>37</v>
+      </c>
+      <c r="K277">
+        <f>+IF(E277="","",VLOOKUP(E277,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L277">
+        <f>+IF(E277="","",VLOOKUP(E277,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M277" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A278" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B278" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C278" s="17" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D278" t="s">
+        <v>38</v>
+      </c>
+      <c r="E278" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F278" s="6">
+        <f>+VLOOKUP(E278,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G278" s="14">
+        <v>72</v>
+      </c>
+      <c r="H278" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I278" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J278" s="12">
+        <v>37</v>
+      </c>
+      <c r="K278">
+        <f>+IF(E278="","",VLOOKUP(E278,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L278">
+        <f>+IF(E278="","",VLOOKUP(E278,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M278" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A279" s="88" t="s">
+        <v>21</v>
+      </c>
+      <c r="B279" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C279" s="17" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D279" t="s">
+        <v>37</v>
+      </c>
+      <c r="E279" s="88" t="s">
+        <v>23</v>
+      </c>
+      <c r="F279" s="6">
+        <f>+VLOOKUP(E279,CATALOGO!G:L,6,0)</f>
+        <v>5</v>
+      </c>
+      <c r="G279" s="14">
+        <v>48</v>
+      </c>
+      <c r="H279" s="14">
+        <v>1</v>
+      </c>
+      <c r="I279" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J279" s="12">
+        <v>37</v>
+      </c>
+      <c r="K279">
+        <f>+IF(E279="","",VLOOKUP(E279,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L279">
+        <f>+IF(E279="","",VLOOKUP(E279,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M279" s="15">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A280" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B280" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C280" s="17" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D280" t="s">
+        <v>37</v>
+      </c>
+      <c r="E280" s="88" t="s">
+        <v>23</v>
+      </c>
+      <c r="F280" s="6">
+        <f>+VLOOKUP(E280,CATALOGO!G:L,6,0)</f>
+        <v>5</v>
+      </c>
+      <c r="G280" s="14">
+        <v>1104</v>
+      </c>
+      <c r="H280" s="14">
+        <v>23</v>
+      </c>
+      <c r="I280" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J280" s="12">
+        <v>37</v>
+      </c>
+      <c r="K280">
+        <f>+IF(E280="","",VLOOKUP(E280,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L280">
+        <f>+IF(E280="","",VLOOKUP(E280,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M280" s="15">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A281" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B281" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C281" s="17" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D281" t="s">
+        <v>37</v>
+      </c>
+      <c r="E281" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F281" s="6">
+        <f>+VLOOKUP(E281,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G281" s="14">
+        <v>1</v>
+      </c>
+      <c r="H281" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I281" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J281" s="12">
+        <v>37</v>
+      </c>
+      <c r="K281">
+        <f>+IF(E281="","",VLOOKUP(E281,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L281">
+        <f>+IF(E281="","",VLOOKUP(E281,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M281" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A282" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B282" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C282" s="17" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D282" t="s">
+        <v>37</v>
+      </c>
+      <c r="E282" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F282" s="6">
+        <f>+VLOOKUP(E282,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G282" s="14">
+        <v>83</v>
+      </c>
+      <c r="H282" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I282" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J282" s="12">
+        <v>37</v>
+      </c>
+      <c r="K282">
+        <f>+IF(E282="","",VLOOKUP(E282,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L282">
+        <f>+IF(E282="","",VLOOKUP(E282,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M282" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A283" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B283" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C283" s="17" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D283" t="s">
+        <v>37</v>
+      </c>
+      <c r="E283" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F283" s="6">
+        <f>+VLOOKUP(E283,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G283" s="14">
+        <v>20</v>
+      </c>
+      <c r="H283" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I283" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J283" s="12">
+        <v>37</v>
+      </c>
+      <c r="K283">
+        <f>+IF(E283="","",VLOOKUP(E283,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L283">
+        <f>+IF(E283="","",VLOOKUP(E283,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M283" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A284" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B284" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C284" s="17" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D284" t="s">
+        <v>37</v>
+      </c>
+      <c r="E284" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F284" s="6">
+        <f>+VLOOKUP(E284,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G284" s="14">
+        <v>50</v>
+      </c>
+      <c r="H284" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I284" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J284" s="12">
+        <v>37</v>
+      </c>
+      <c r="K284">
+        <f>+IF(E284="","",VLOOKUP(E284,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L284">
+        <f>+IF(E284="","",VLOOKUP(E284,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M284" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A285" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B285" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C285" s="17" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D285" t="s">
+        <v>17</v>
+      </c>
+      <c r="E285" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="F285" s="6">
+        <f>+VLOOKUP(E285,CATALOGO!G:L,6,0)</f>
+        <v>3</v>
+      </c>
+      <c r="G285" s="14">
+        <v>1056</v>
+      </c>
+      <c r="H285" s="14">
+        <v>22</v>
+      </c>
+      <c r="I285" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J285" s="12">
+        <v>37</v>
+      </c>
+      <c r="K285">
+        <f>+IF(E285="","",VLOOKUP(E285,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L285">
+        <f>+IF(E285="","",VLOOKUP(E285,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M285" s="15">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A286" s="88" t="s">
+        <v>18</v>
+      </c>
+      <c r="B286" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C286" s="17" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D286" t="s">
+        <v>17</v>
+      </c>
+      <c r="E286" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="F286" s="6">
+        <f>+VLOOKUP(E286,CATALOGO!G:L,6,0)</f>
+        <v>3</v>
+      </c>
+      <c r="G286" s="14">
+        <v>96</v>
+      </c>
+      <c r="H286" s="14">
+        <v>2</v>
+      </c>
+      <c r="I286" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J286" s="12">
+        <v>37</v>
+      </c>
+      <c r="K286">
+        <f>+IF(E286="","",VLOOKUP(E286,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L286">
+        <f>+IF(E286="","",VLOOKUP(E286,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M286" s="15">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="287" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A287" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B287" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C287" s="17" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D287" t="s">
+        <v>17</v>
+      </c>
+      <c r="E287" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F287" s="6">
+        <f>+VLOOKUP(E287,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G287" s="14">
+        <v>1</v>
+      </c>
+      <c r="H287" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I287" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J287" s="12">
+        <v>37</v>
+      </c>
+      <c r="K287">
+        <f>+IF(E287="","",VLOOKUP(E287,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L287">
+        <f>+IF(E287="","",VLOOKUP(E287,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M287" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="288" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A288" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B288" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C288" s="17" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D288" t="s">
+        <v>17</v>
+      </c>
+      <c r="E288" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F288" s="6">
+        <f>+VLOOKUP(E288,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G288" s="14">
+        <v>52</v>
+      </c>
+      <c r="H288" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I288" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J288" s="12">
+        <v>37</v>
+      </c>
+      <c r="K288">
+        <f>+IF(E288="","",VLOOKUP(E288,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L288">
+        <f>+IF(E288="","",VLOOKUP(E288,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M288" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="289" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A289" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B289" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C289" s="17" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D289" t="s">
+        <v>17</v>
+      </c>
+      <c r="E289" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F289" s="6">
+        <f>+VLOOKUP(E289,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G289" s="14">
+        <v>76</v>
+      </c>
+      <c r="H289" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I289" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J289" s="12">
+        <v>37</v>
+      </c>
+      <c r="K289">
+        <f>+IF(E289="","",VLOOKUP(E289,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L289">
+        <f>+IF(E289="","",VLOOKUP(E289,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M289" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="290" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A290" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B290" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C290" s="17" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D290" t="s">
+        <v>17</v>
+      </c>
+      <c r="E290" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F290" s="6">
+        <f>+VLOOKUP(E290,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G290" s="14">
+        <v>24</v>
+      </c>
+      <c r="H290" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I290" s="16">
+        <v>46276</v>
+      </c>
+      <c r="J290" s="12">
+        <v>37</v>
+      </c>
+      <c r="K290">
+        <f>+IF(E290="","",VLOOKUP(E290,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L290">
+        <f>+IF(E290="","",VLOOKUP(E290,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M290" s="15">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="291" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A291" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B291" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C291" s="17" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D291" t="s">
+        <v>54</v>
+      </c>
+      <c r="E291" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F291" s="6">
+        <f>+VLOOKUP(E291,CATALOGO!G:L,6,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G291" s="14">
+        <v>960</v>
+      </c>
+      <c r="H291" s="14">
+        <v>20</v>
+      </c>
+      <c r="I291" s="16">
+        <v>46277</v>
+      </c>
+      <c r="J291" s="12">
+        <v>37</v>
+      </c>
+      <c r="K291">
+        <f>+IF(E291="","",VLOOKUP(E291,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L291">
+        <f>+IF(E291="","",VLOOKUP(E291,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M291" s="15">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A292" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B292" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C292" s="17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E292" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F292" s="6">
+        <f>+VLOOKUP(E292,CATALOGO!G:L,6,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G292" s="14">
+        <v>960</v>
+      </c>
+      <c r="H292" s="14">
+        <v>20</v>
+      </c>
+      <c r="I292" s="16">
+        <v>46277</v>
+      </c>
+      <c r="J292" s="12">
+        <v>37</v>
+      </c>
+      <c r="K292">
+        <f>+IF(E292="","",VLOOKUP(E292,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L292">
+        <f>+IF(E292="","",VLOOKUP(E292,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M292" s="15">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A293" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="B293" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C293" s="17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E293" s="88" t="s">
+        <v>44</v>
+      </c>
+      <c r="F293" s="6">
+        <f>+VLOOKUP(E293,CATALOGO!G:L,6,0)</f>
+        <v>1</v>
+      </c>
+      <c r="G293" s="14">
+        <v>480</v>
+      </c>
+      <c r="H293" s="14">
+        <v>10</v>
+      </c>
+      <c r="I293" s="16">
+        <v>46277</v>
+      </c>
+      <c r="J293" s="12">
+        <v>37</v>
+      </c>
+      <c r="K293">
+        <f>+IF(E293="","",VLOOKUP(E293,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L293">
+        <f>+IF(E293="","",VLOOKUP(E293,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M293" s="15">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A294" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B294" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C294" s="17" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D294" t="s">
+        <v>53</v>
+      </c>
+      <c r="E294" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F294" s="6">
+        <f>+VLOOKUP(E294,CATALOGO!G:L,6,0)</f>
+        <v>8</v>
+      </c>
+      <c r="G294" s="14">
+        <v>960</v>
+      </c>
+      <c r="H294" s="14">
+        <v>20</v>
+      </c>
+      <c r="I294" s="16">
+        <v>46277</v>
+      </c>
+      <c r="J294" s="12">
+        <v>37</v>
+      </c>
+      <c r="K294">
+        <f>+IF(E294="","",VLOOKUP(E294,CATALOGO!G:I,2,0))</f>
+        <v>3</v>
+      </c>
+      <c r="L294">
+        <f>+IF(E294="","",VLOOKUP(E294,CATALOGO!G:I,3,0))</f>
+        <v>72</v>
+      </c>
+      <c r="M294" s="15">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A295" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B295" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C295" s="17" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D295" t="s">
+        <v>53</v>
+      </c>
+      <c r="E295" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F295" s="6">
+        <f>+VLOOKUP(E295,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G295" s="14">
+        <v>1</v>
+      </c>
+      <c r="H295" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I295" s="16">
+        <v>46277</v>
+      </c>
+      <c r="J295" s="12">
+        <v>37</v>
+      </c>
+      <c r="K295">
+        <f>+IF(E295="","",VLOOKUP(E295,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L295">
+        <f>+IF(E295="","",VLOOKUP(E295,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M295" s="15" t="e">
+        <f>+[1]!Tabla1[[#This Row],[Fecha de empaque]]+2</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A296" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B296" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C296" s="17" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D296" t="s">
+        <v>53</v>
+      </c>
+      <c r="E296" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F296" s="6">
+        <f>+VLOOKUP(E296,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G296" s="14">
+        <v>52</v>
+      </c>
+      <c r="H296" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I296" s="16">
+        <v>46277</v>
+      </c>
+      <c r="J296" s="12">
+        <v>37</v>
+      </c>
+      <c r="K296">
+        <f>+IF(E296="","",VLOOKUP(E296,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L296">
+        <f>+IF(E296="","",VLOOKUP(E296,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M296" s="15" t="e">
+        <f>+[1]!Tabla1[[#This Row],[Fecha de empaque]]+2</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A297" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B297" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C297" s="17" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D297" t="s">
+        <v>53</v>
+      </c>
+      <c r="E297" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F297" s="6">
+        <f>+VLOOKUP(E297,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G297" s="14">
+        <v>76</v>
+      </c>
+      <c r="H297" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I297" s="16">
+        <v>46277</v>
+      </c>
+      <c r="J297" s="12">
+        <v>37</v>
+      </c>
+      <c r="K297">
+        <f>+IF(E297="","",VLOOKUP(E297,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L297">
+        <f>+IF(E297="","",VLOOKUP(E297,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M297" s="15" t="e">
+        <f>+[1]!Tabla1[[#This Row],[Fecha de empaque]]+2</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A298" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B298" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C298" s="17" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D298" t="s">
+        <v>53</v>
+      </c>
+      <c r="E298" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F298" s="6">
+        <f>+VLOOKUP(E298,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G298" s="14">
+        <v>24</v>
+      </c>
+      <c r="H298" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I298" s="16">
+        <v>46277</v>
+      </c>
+      <c r="J298" s="12">
+        <v>37</v>
+      </c>
+      <c r="K298">
+        <f>+IF(E298="","",VLOOKUP(E298,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L298">
+        <f>+IF(E298="","",VLOOKUP(E298,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M298" s="15" t="e">
+        <f>+[1]!Tabla1[[#This Row],[Fecha de empaque]]+2</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A299" s="88" t="s">
+        <v>18</v>
+      </c>
+      <c r="B299" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C299" s="17" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D299" t="s">
+        <v>17</v>
+      </c>
+      <c r="E299" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="F299" s="6">
+        <f>+VLOOKUP(E299,CATALOGO!G:L,6,0)</f>
+        <v>6</v>
+      </c>
+      <c r="G299" s="14">
+        <v>288</v>
+      </c>
+      <c r="H299" s="14">
+        <v>6</v>
+      </c>
+      <c r="I299" s="16">
+        <v>46277</v>
+      </c>
+      <c r="J299" s="12">
+        <v>37</v>
+      </c>
+      <c r="K299">
+        <f>+IF(E299="","",VLOOKUP(E299,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L299">
+        <f>+IF(E299="","",VLOOKUP(E299,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M299" s="15">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A300" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="B300" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C300" s="17" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D300" t="s">
+        <v>17</v>
+      </c>
+      <c r="E300" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="F300" s="6">
+        <f>+VLOOKUP(E300,CATALOGO!G:L,6,0)</f>
+        <v>6</v>
+      </c>
+      <c r="G300" s="14">
+        <v>864</v>
+      </c>
+      <c r="H300" s="14">
+        <v>18</v>
+      </c>
+      <c r="I300" s="16">
+        <v>46277</v>
+      </c>
+      <c r="J300" s="12">
+        <v>37</v>
+      </c>
+      <c r="K300">
+        <f>+IF(E300="","",VLOOKUP(E300,CATALOGO!G:I,2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L300">
+        <f>+IF(E300="","",VLOOKUP(E300,CATALOGO!G:I,3,0))</f>
+        <v>24</v>
+      </c>
+      <c r="M300" s="15">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A301" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B301" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C301" s="17" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D301" t="s">
+        <v>17</v>
+      </c>
+      <c r="E301" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F301" s="6">
+        <f>+VLOOKUP(E301,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G301" s="14">
+        <v>1</v>
+      </c>
+      <c r="H301" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I301" s="16">
+        <v>46277</v>
+      </c>
+      <c r="J301" s="12">
+        <v>37</v>
+      </c>
+      <c r="K301">
+        <f>+IF(E301="","",VLOOKUP(E301,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L301">
+        <f>+IF(E301="","",VLOOKUP(E301,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M301" s="15" t="e">
+        <f>+[1]!Tabla1[[#This Row],[Fecha de empaque]]+2</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A302" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B302" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C302" s="17" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D302" t="s">
+        <v>17</v>
+      </c>
+      <c r="E302" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F302" s="6">
+        <f>+VLOOKUP(E302,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G302" s="14">
+        <v>52</v>
+      </c>
+      <c r="H302" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I302" s="16">
+        <v>46277</v>
+      </c>
+      <c r="J302" s="12">
+        <v>37</v>
+      </c>
+      <c r="K302">
+        <f>+IF(E302="","",VLOOKUP(E302,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L302">
+        <f>+IF(E302="","",VLOOKUP(E302,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M302" s="15" t="e">
+        <f>+[1]!Tabla1[[#This Row],[Fecha de empaque]]+2</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A303" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B303" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C303" s="17" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D303" t="s">
+        <v>17</v>
+      </c>
+      <c r="E303" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F303" s="6">
+        <f>+VLOOKUP(E303,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G303" s="14">
+        <v>76</v>
+      </c>
+      <c r="H303" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I303" s="16">
+        <v>46277</v>
+      </c>
+      <c r="J303" s="12">
+        <v>37</v>
+      </c>
+      <c r="K303">
+        <f>+IF(E303="","",VLOOKUP(E303,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L303">
+        <f>+IF(E303="","",VLOOKUP(E303,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M303" s="15" t="e">
+        <f>+[1]!Tabla1[[#This Row],[Fecha de empaque]]+2</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A304" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B304" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C304" s="17" t="s">
+        <v>1521</v>
+      </c>
+      <c r="D304" t="s">
+        <v>17</v>
+      </c>
+      <c r="E304" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F304" s="6">
+        <f>+VLOOKUP(E304,CATALOGO!G:L,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G304" s="14">
+        <v>24</v>
+      </c>
+      <c r="H304" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I304" s="16">
+        <v>46277</v>
+      </c>
+      <c r="J304" s="12">
+        <v>37</v>
+      </c>
+      <c r="K304">
+        <f>+IF(E304="","",VLOOKUP(E304,CATALOGO!G:I,2,0))</f>
+        <v>1.5</v>
+      </c>
+      <c r="L304">
+        <f>+IF(E304="","",VLOOKUP(E304,CATALOGO!G:I,3,0))</f>
+        <v>36</v>
+      </c>
+      <c r="M304" s="15" t="e">
+        <f>+[1]!Tabla1[[#This Row],[Fecha de empaque]]+2</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M135" xr:uid="{F6943C4E-D0C1-4399-9277-8C3BA29014B7}"/>
-  <conditionalFormatting sqref="M2:M160">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+  <conditionalFormatting sqref="M2:M304">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M161:M304">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21542,7 +28188,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B351">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
+    <cfRule type="containsBlanks" dxfId="1" priority="1">
       <formula>LEN(TRIM(B351))=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22199,12 +28845,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9ec7a165-d323-4302-8043-ea580ce1e37b" xsi:nil="true"/>
+    <_ModernAudienceTargetUserField xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ModernAudienceTargetUserField>
+    <Audiencias_x0020_de_x0020_destino xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22459,29 +29116,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9ec7a165-d323-4302-8043-ea580ce1e37b" xsi:nil="true"/>
-    <_ModernAudienceTargetUserField xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ModernAudienceTargetUserField>
-    <Audiencias_x0020_de_x0020_destino xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AE2DB07-E1EE-4AEB-80E7-74D3285DBEFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA9869F1-282E-4391-9BF8-BCB60A0A8B6F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac"/>
+    <ds:schemaRef ds:uri="9ec7a165-d323-4302-8043-ea580ce1e37b"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -22506,12 +29155,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA9869F1-282E-4391-9BF8-BCB60A0A8B6F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AE2DB07-E1EE-4AEB-80E7-74D3285DBEFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac"/>
-    <ds:schemaRef ds:uri="9ec7a165-d323-4302-8043-ea580ce1e37b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/PLANEACION_SEMANAL 1.xlsx
+++ b/PLANEACION_SEMANAL 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chanitosfrutas.sharepoint.com/sites/04.Logstica/Documentos compartidos/General/Pre-enfrío/09. Desarrollos/Planeacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="509" documentId="8_{545E5EC0-B69F-4327-BF2C-9EFD71AFF5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C6C0B5C-5B7F-4C6C-ADD0-4F4E12E29D95}"/>
+  <xr:revisionPtr revIDLastSave="510" documentId="8_{545E5EC0-B69F-4327-BF2C-9EFD71AFF5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E9D9929-7A35-4D6C-A479-5EB0300DA938}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D41B2D9D-66D1-4881-AE1E-852E308D9588}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="CATALOGO" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PLANEACION!$A$1:$N$313</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PLANEACION!$A$1:$N$168</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -5285,7 +5285,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6943C4E-D0C1-4399-9277-8C3BA29014B7}">
-  <dimension ref="A1:N313"/>
+  <dimension ref="A1:N169"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" style="6" customWidth="1"/>
@@ -11990,7 +11990,7 @@
         <v>46276</v>
       </c>
       <c r="J142" s="12">
-        <f t="shared" ref="J142:J205" si="3">+WEEKNUM(I142)</f>
+        <f t="shared" ref="J142:J168" si="3">+WEEKNUM(I142)</f>
         <v>37</v>
       </c>
       <c r="K142">
@@ -13229,4069 +13229,10 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="169" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="13"/>
-      <c r="B169" s="13"/>
-      <c r="C169" s="17"/>
-      <c r="E169" s="88"/>
-      <c r="F169" s="6" t="e">
-        <f>+VLOOKUP(E169,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G169" s="14"/>
-      <c r="H169" s="14"/>
-      <c r="I169" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J169" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K169" t="str">
-        <f>+IF(E169="","",VLOOKUP(E169,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L169" t="str">
-        <f>+IF(E169="","",VLOOKUP(E169,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M169" s="15"/>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A170" s="13"/>
-      <c r="B170" s="13"/>
-      <c r="C170" s="17"/>
-      <c r="E170" s="88"/>
-      <c r="F170" s="6" t="e">
-        <f>+VLOOKUP(E170,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G170" s="14"/>
-      <c r="H170" s="14"/>
-      <c r="I170" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J170" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K170" t="str">
-        <f>+IF(E170="","",VLOOKUP(E170,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L170" t="str">
-        <f>+IF(E170="","",VLOOKUP(E170,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M170" s="15"/>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A171" s="13"/>
-      <c r="B171" s="13"/>
-      <c r="C171" s="17"/>
-      <c r="E171" s="88"/>
-      <c r="F171" s="6" t="e">
-        <f>+VLOOKUP(E171,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G171" s="14"/>
-      <c r="H171" s="14"/>
-      <c r="I171" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J171" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K171" t="str">
-        <f>+IF(E171="","",VLOOKUP(E171,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L171" t="str">
-        <f>+IF(E171="","",VLOOKUP(E171,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M171" s="15"/>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A172" s="13"/>
-      <c r="B172" s="13"/>
-      <c r="C172" s="17"/>
-      <c r="E172" s="88"/>
-      <c r="F172" s="6" t="e">
-        <f>+VLOOKUP(E172,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G172" s="14"/>
-      <c r="H172" s="14"/>
-      <c r="I172" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J172" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K172" t="str">
-        <f>+IF(E172="","",VLOOKUP(E172,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L172" t="str">
-        <f>+IF(E172="","",VLOOKUP(E172,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M172" s="15"/>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A173" s="13"/>
-      <c r="B173" s="13"/>
-      <c r="C173" s="17"/>
-      <c r="E173" s="88"/>
-      <c r="F173" s="6" t="e">
-        <f>+VLOOKUP(E173,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G173" s="14"/>
-      <c r="H173" s="14"/>
-      <c r="I173" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J173" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K173" t="str">
-        <f>+IF(E173="","",VLOOKUP(E173,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L173" t="str">
-        <f>+IF(E173="","",VLOOKUP(E173,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M173" s="15"/>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A174" s="13"/>
-      <c r="B174" s="13"/>
-      <c r="C174" s="17"/>
-      <c r="E174" s="88"/>
-      <c r="F174" s="6" t="e">
-        <f>+VLOOKUP(E174,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G174" s="14"/>
-      <c r="H174" s="14"/>
-      <c r="I174" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J174" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K174" t="str">
-        <f>+IF(E174="","",VLOOKUP(E174,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L174" t="str">
-        <f>+IF(E174="","",VLOOKUP(E174,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M174" s="15"/>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A175" s="13"/>
-      <c r="B175" s="13"/>
-      <c r="C175" s="17"/>
-      <c r="E175" s="88"/>
-      <c r="F175" s="6" t="e">
-        <f>+VLOOKUP(E175,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G175" s="14"/>
-      <c r="H175" s="14"/>
-      <c r="I175" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J175" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K175" t="str">
-        <f>+IF(E175="","",VLOOKUP(E175,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L175" t="str">
-        <f>+IF(E175="","",VLOOKUP(E175,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M175" s="15"/>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A176" s="13"/>
-      <c r="B176" s="13"/>
-      <c r="C176" s="17"/>
-      <c r="E176" s="88"/>
-      <c r="F176" s="6" t="e">
-        <f>+VLOOKUP(E176,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G176" s="14"/>
-      <c r="H176" s="14"/>
-      <c r="I176" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J176" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K176" t="str">
-        <f>+IF(E176="","",VLOOKUP(E176,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L176" t="str">
-        <f>+IF(E176="","",VLOOKUP(E176,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M176" s="15"/>
-    </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A177" s="13"/>
-      <c r="B177" s="13"/>
-      <c r="C177" s="17"/>
-      <c r="E177" s="88"/>
-      <c r="F177" s="6" t="e">
-        <f>+VLOOKUP(E177,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G177" s="14"/>
-      <c r="H177" s="14"/>
-      <c r="I177" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J177" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K177" t="str">
-        <f>+IF(E177="","",VLOOKUP(E177,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L177" t="str">
-        <f>+IF(E177="","",VLOOKUP(E177,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M177" s="15"/>
-    </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A178" s="13"/>
-      <c r="B178" s="13"/>
-      <c r="C178" s="17"/>
-      <c r="E178" s="88"/>
-      <c r="F178" s="6" t="e">
-        <f>+VLOOKUP(E178,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G178" s="14"/>
-      <c r="H178" s="14"/>
-      <c r="I178" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J178" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K178" t="str">
-        <f>+IF(E178="","",VLOOKUP(E178,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L178" t="str">
-        <f>+IF(E178="","",VLOOKUP(E178,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M178" s="15"/>
-    </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A179" s="13"/>
-      <c r="B179" s="13"/>
-      <c r="C179" s="17"/>
-      <c r="E179" s="88"/>
-      <c r="F179" s="6" t="e">
-        <f>+VLOOKUP(E179,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G179" s="14"/>
-      <c r="H179" s="14"/>
-      <c r="I179" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J179" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K179" t="str">
-        <f>+IF(E179="","",VLOOKUP(E179,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L179" t="str">
-        <f>+IF(E179="","",VLOOKUP(E179,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M179" s="15"/>
-    </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A180" s="13"/>
-      <c r="B180" s="13"/>
-      <c r="C180" s="17"/>
-      <c r="E180" s="88"/>
-      <c r="F180" s="6" t="e">
-        <f>+VLOOKUP(E180,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G180" s="14"/>
-      <c r="H180" s="14"/>
-      <c r="I180" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J180" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K180" t="str">
-        <f>+IF(E180="","",VLOOKUP(E180,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L180" t="str">
-        <f>+IF(E180="","",VLOOKUP(E180,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M180" s="15"/>
-    </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A181" s="13"/>
-      <c r="B181" s="13"/>
-      <c r="C181" s="17"/>
-      <c r="E181" s="88"/>
-      <c r="F181" s="6" t="e">
-        <f>+VLOOKUP(E181,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G181" s="14"/>
-      <c r="H181" s="14"/>
-      <c r="I181" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J181" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K181" t="str">
-        <f>+IF(E181="","",VLOOKUP(E181,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L181" t="str">
-        <f>+IF(E181="","",VLOOKUP(E181,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M181" s="15"/>
-    </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A182" s="13"/>
-      <c r="B182" s="13"/>
-      <c r="C182" s="17"/>
-      <c r="E182" s="88"/>
-      <c r="F182" s="6" t="e">
-        <f>+VLOOKUP(E182,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G182" s="14"/>
-      <c r="H182" s="14"/>
-      <c r="I182" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J182" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K182" t="str">
-        <f>+IF(E182="","",VLOOKUP(E182,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L182" t="str">
-        <f>+IF(E182="","",VLOOKUP(E182,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M182" s="15"/>
-    </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A183" s="13"/>
-      <c r="B183" s="13"/>
-      <c r="C183" s="17"/>
-      <c r="E183" s="88"/>
-      <c r="F183" s="6" t="e">
-        <f>+VLOOKUP(E183,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G183" s="14"/>
-      <c r="H183" s="14"/>
-      <c r="I183" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J183" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K183" t="str">
-        <f>+IF(E183="","",VLOOKUP(E183,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L183" t="str">
-        <f>+IF(E183="","",VLOOKUP(E183,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M183" s="15"/>
-    </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A184" s="13"/>
-      <c r="B184" s="13"/>
-      <c r="C184" s="17"/>
-      <c r="E184" s="88"/>
-      <c r="F184" s="6" t="e">
-        <f>+VLOOKUP(E184,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G184" s="14"/>
-      <c r="H184" s="14"/>
-      <c r="I184" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J184" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K184" t="str">
-        <f>+IF(E184="","",VLOOKUP(E184,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L184" t="str">
-        <f>+IF(E184="","",VLOOKUP(E184,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M184" s="15"/>
-    </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A185" s="13"/>
-      <c r="B185" s="13"/>
-      <c r="C185" s="17"/>
-      <c r="E185" s="88"/>
-      <c r="F185" s="6" t="e">
-        <f>+VLOOKUP(E185,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G185" s="14"/>
-      <c r="H185" s="14"/>
-      <c r="I185" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J185" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K185" t="str">
-        <f>+IF(E185="","",VLOOKUP(E185,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L185" t="str">
-        <f>+IF(E185="","",VLOOKUP(E185,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M185" s="15"/>
-    </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A186" s="13"/>
-      <c r="B186" s="13"/>
-      <c r="C186" s="17"/>
-      <c r="E186" s="88"/>
-      <c r="F186" s="6" t="e">
-        <f>+VLOOKUP(E186,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G186" s="14"/>
-      <c r="H186" s="14"/>
-      <c r="I186" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J186" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K186" t="str">
-        <f>+IF(E186="","",VLOOKUP(E186,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L186" t="str">
-        <f>+IF(E186="","",VLOOKUP(E186,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M186" s="15"/>
-    </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A187" s="13"/>
-      <c r="B187" s="13"/>
-      <c r="C187" s="17"/>
-      <c r="E187" s="88"/>
-      <c r="F187" s="6" t="e">
-        <f>+VLOOKUP(E187,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G187" s="14"/>
-      <c r="H187" s="14"/>
-      <c r="I187" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J187" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K187" t="str">
-        <f>+IF(E187="","",VLOOKUP(E187,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L187" t="str">
-        <f>+IF(E187="","",VLOOKUP(E187,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M187" s="15"/>
-    </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A188" s="13"/>
-      <c r="B188" s="13"/>
-      <c r="C188" s="17"/>
-      <c r="E188" s="88"/>
-      <c r="F188" s="6" t="e">
-        <f>+VLOOKUP(E188,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G188" s="14"/>
-      <c r="H188" s="14"/>
-      <c r="I188" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J188" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K188" t="str">
-        <f>+IF(E188="","",VLOOKUP(E188,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L188" t="str">
-        <f>+IF(E188="","",VLOOKUP(E188,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M188" s="15"/>
-    </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A189" s="13"/>
-      <c r="B189" s="13"/>
-      <c r="C189" s="17"/>
-      <c r="E189" s="88"/>
-      <c r="F189" s="6" t="e">
-        <f>+VLOOKUP(E189,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G189" s="14"/>
-      <c r="H189" s="14"/>
-      <c r="I189" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J189" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K189" t="str">
-        <f>+IF(E189="","",VLOOKUP(E189,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L189" t="str">
-        <f>+IF(E189="","",VLOOKUP(E189,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M189" s="15"/>
-    </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A190" s="13"/>
-      <c r="B190" s="13"/>
-      <c r="C190" s="17"/>
-      <c r="E190" s="88"/>
-      <c r="F190" s="6" t="e">
-        <f>+VLOOKUP(E190,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G190" s="14"/>
-      <c r="H190" s="14"/>
-      <c r="I190" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J190" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K190" t="str">
-        <f>+IF(E190="","",VLOOKUP(E190,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L190" t="str">
-        <f>+IF(E190="","",VLOOKUP(E190,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M190" s="15"/>
-    </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A191" s="13"/>
-      <c r="B191" s="13"/>
-      <c r="C191" s="17"/>
-      <c r="E191" s="88"/>
-      <c r="F191" s="6" t="e">
-        <f>+VLOOKUP(E191,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G191" s="14"/>
-      <c r="H191" s="14"/>
-      <c r="I191" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J191" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K191" t="str">
-        <f>+IF(E191="","",VLOOKUP(E191,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L191" t="str">
-        <f>+IF(E191="","",VLOOKUP(E191,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M191" s="15"/>
-    </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A192" s="13"/>
-      <c r="B192" s="13"/>
-      <c r="C192" s="17"/>
-      <c r="E192" s="88"/>
-      <c r="F192" s="6" t="e">
-        <f>+VLOOKUP(E192,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G192" s="14"/>
-      <c r="H192" s="14"/>
-      <c r="I192" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J192" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K192" t="str">
-        <f>+IF(E192="","",VLOOKUP(E192,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L192" t="str">
-        <f>+IF(E192="","",VLOOKUP(E192,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M192" s="15"/>
-    </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A193" s="13"/>
-      <c r="B193" s="13"/>
-      <c r="C193" s="17"/>
-      <c r="E193" s="88"/>
-      <c r="F193" s="6" t="e">
-        <f>+VLOOKUP(E193,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G193" s="14"/>
-      <c r="H193" s="14"/>
-      <c r="I193" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J193" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K193" t="str">
-        <f>+IF(E193="","",VLOOKUP(E193,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L193" t="str">
-        <f>+IF(E193="","",VLOOKUP(E193,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M193" s="15"/>
-    </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A194" s="13"/>
-      <c r="B194" s="13"/>
-      <c r="C194" s="17"/>
-      <c r="E194" s="88"/>
-      <c r="F194" s="6" t="e">
-        <f>+VLOOKUP(E194,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G194" s="14"/>
-      <c r="H194" s="14"/>
-      <c r="I194" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J194" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K194" t="str">
-        <f>+IF(E194="","",VLOOKUP(E194,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L194" t="str">
-        <f>+IF(E194="","",VLOOKUP(E194,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M194" s="15"/>
-    </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A195" s="13"/>
-      <c r="B195" s="13"/>
-      <c r="C195" s="17"/>
-      <c r="E195" s="88"/>
-      <c r="F195" s="6" t="e">
-        <f>+VLOOKUP(E195,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G195" s="14"/>
-      <c r="H195" s="14"/>
-      <c r="I195" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J195" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K195" t="str">
-        <f>+IF(E195="","",VLOOKUP(E195,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L195" t="str">
-        <f>+IF(E195="","",VLOOKUP(E195,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M195" s="15"/>
-    </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A196" s="13"/>
-      <c r="B196" s="13"/>
-      <c r="C196" s="17"/>
-      <c r="E196" s="88"/>
-      <c r="F196" s="6" t="e">
-        <f>+VLOOKUP(E196,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G196" s="14"/>
-      <c r="H196" s="14"/>
-      <c r="I196" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J196" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K196" t="str">
-        <f>+IF(E196="","",VLOOKUP(E196,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L196" t="str">
-        <f>+IF(E196="","",VLOOKUP(E196,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M196" s="15"/>
-    </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A197" s="13"/>
-      <c r="B197" s="13"/>
-      <c r="C197" s="17"/>
-      <c r="E197" s="88"/>
-      <c r="F197" s="6" t="e">
-        <f>+VLOOKUP(E197,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G197" s="14"/>
-      <c r="H197" s="14"/>
-      <c r="I197" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J197" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K197" t="str">
-        <f>+IF(E197="","",VLOOKUP(E197,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L197" t="str">
-        <f>+IF(E197="","",VLOOKUP(E197,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M197" s="15"/>
-    </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A198" s="13"/>
-      <c r="B198" s="13"/>
-      <c r="C198" s="17"/>
-      <c r="E198" s="88"/>
-      <c r="F198" s="6" t="e">
-        <f>+VLOOKUP(E198,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G198" s="14"/>
-      <c r="H198" s="14"/>
-      <c r="I198" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J198" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K198" t="str">
-        <f>+IF(E198="","",VLOOKUP(E198,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L198" t="str">
-        <f>+IF(E198="","",VLOOKUP(E198,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M198" s="15"/>
-    </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A199" s="13"/>
-      <c r="B199" s="13"/>
-      <c r="C199" s="17"/>
-      <c r="E199" s="88"/>
-      <c r="F199" s="6" t="e">
-        <f>+VLOOKUP(E199,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G199" s="14"/>
-      <c r="H199" s="14"/>
-      <c r="I199" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J199" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K199" t="str">
-        <f>+IF(E199="","",VLOOKUP(E199,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L199" t="str">
-        <f>+IF(E199="","",VLOOKUP(E199,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M199" s="15"/>
-    </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A200" s="13"/>
-      <c r="B200" s="13"/>
-      <c r="C200" s="17"/>
-      <c r="E200" s="88"/>
-      <c r="F200" s="6" t="e">
-        <f>+VLOOKUP(E200,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G200" s="14"/>
-      <c r="H200" s="14"/>
-      <c r="I200" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J200" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K200" t="str">
-        <f>+IF(E200="","",VLOOKUP(E200,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L200" t="str">
-        <f>+IF(E200="","",VLOOKUP(E200,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M200" s="15"/>
-    </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A201" s="13"/>
-      <c r="B201" s="13"/>
-      <c r="C201" s="17"/>
-      <c r="E201" s="88"/>
-      <c r="F201" s="6" t="e">
-        <f>+VLOOKUP(E201,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G201" s="14"/>
-      <c r="H201" s="14"/>
-      <c r="I201" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J201" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K201" t="str">
-        <f>+IF(E201="","",VLOOKUP(E201,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L201" t="str">
-        <f>+IF(E201="","",VLOOKUP(E201,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M201" s="15"/>
-    </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A202" s="13"/>
-      <c r="B202" s="13"/>
-      <c r="C202" s="17"/>
-      <c r="E202" s="88"/>
-      <c r="F202" s="6" t="e">
-        <f>+VLOOKUP(E202,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G202" s="14"/>
-      <c r="H202" s="14"/>
-      <c r="I202" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J202" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K202" t="str">
-        <f>+IF(E202="","",VLOOKUP(E202,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L202" t="str">
-        <f>+IF(E202="","",VLOOKUP(E202,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M202" s="15"/>
-    </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A203" s="13"/>
-      <c r="B203" s="13"/>
-      <c r="C203" s="17"/>
-      <c r="E203" s="88"/>
-      <c r="F203" s="6" t="e">
-        <f>+VLOOKUP(E203,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G203" s="14"/>
-      <c r="H203" s="14"/>
-      <c r="I203" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J203" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K203" t="str">
-        <f>+IF(E203="","",VLOOKUP(E203,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L203" t="str">
-        <f>+IF(E203="","",VLOOKUP(E203,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M203" s="15"/>
-    </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A204" s="13"/>
-      <c r="B204" s="13"/>
-      <c r="C204" s="17"/>
-      <c r="E204" s="88"/>
-      <c r="F204" s="6" t="e">
-        <f>+VLOOKUP(E204,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G204" s="14"/>
-      <c r="H204" s="14"/>
-      <c r="I204" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J204" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K204" t="str">
-        <f>+IF(E204="","",VLOOKUP(E204,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L204" t="str">
-        <f>+IF(E204="","",VLOOKUP(E204,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M204" s="15"/>
-    </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A205" s="13"/>
-      <c r="B205" s="13"/>
-      <c r="C205" s="17"/>
-      <c r="E205" s="88"/>
-      <c r="F205" s="6" t="e">
-        <f>+VLOOKUP(E205,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G205" s="14"/>
-      <c r="H205" s="14"/>
-      <c r="I205" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J205" s="12">
-        <f t="shared" si="3"/>
-        <v>37</v>
-      </c>
-      <c r="K205" t="str">
-        <f>+IF(E205="","",VLOOKUP(E205,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L205" t="str">
-        <f>+IF(E205="","",VLOOKUP(E205,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M205" s="15"/>
-    </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A206" s="13"/>
-      <c r="B206" s="13"/>
-      <c r="C206" s="17"/>
-      <c r="E206" s="88"/>
-      <c r="F206" s="6" t="e">
-        <f>+VLOOKUP(E206,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G206" s="14"/>
-      <c r="H206" s="14"/>
-      <c r="I206" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J206" s="12">
-        <f t="shared" ref="J206:J269" si="4">+WEEKNUM(I206)</f>
-        <v>37</v>
-      </c>
-      <c r="K206" t="str">
-        <f>+IF(E206="","",VLOOKUP(E206,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L206" t="str">
-        <f>+IF(E206="","",VLOOKUP(E206,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M206" s="15"/>
-    </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A207" s="13"/>
-      <c r="B207" s="13"/>
-      <c r="C207" s="17"/>
-      <c r="E207" s="88"/>
-      <c r="F207" s="6" t="e">
-        <f>+VLOOKUP(E207,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G207" s="14"/>
-      <c r="H207" s="14"/>
-      <c r="I207" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J207" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K207" t="str">
-        <f>+IF(E207="","",VLOOKUP(E207,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L207" t="str">
-        <f>+IF(E207="","",VLOOKUP(E207,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M207" s="15"/>
-    </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A208" s="13"/>
-      <c r="B208" s="13"/>
-      <c r="C208" s="17"/>
-      <c r="E208" s="88"/>
-      <c r="F208" s="6" t="e">
-        <f>+VLOOKUP(E208,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G208" s="14"/>
-      <c r="H208" s="14"/>
-      <c r="I208" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J208" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K208" t="str">
-        <f>+IF(E208="","",VLOOKUP(E208,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L208" t="str">
-        <f>+IF(E208="","",VLOOKUP(E208,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M208" s="15"/>
-    </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A209" s="13"/>
-      <c r="B209" s="13"/>
-      <c r="C209" s="17"/>
-      <c r="E209" s="88"/>
-      <c r="F209" s="6" t="e">
-        <f>+VLOOKUP(E209,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G209" s="14"/>
-      <c r="H209" s="14"/>
-      <c r="I209" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J209" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K209" t="str">
-        <f>+IF(E209="","",VLOOKUP(E209,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L209" t="str">
-        <f>+IF(E209="","",VLOOKUP(E209,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M209" s="15"/>
-    </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A210" s="13"/>
-      <c r="B210" s="13"/>
-      <c r="C210" s="17"/>
-      <c r="E210" s="88"/>
-      <c r="F210" s="6" t="e">
-        <f>+VLOOKUP(E210,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G210" s="14"/>
-      <c r="H210" s="14"/>
-      <c r="I210" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J210" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K210" t="str">
-        <f>+IF(E210="","",VLOOKUP(E210,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L210" t="str">
-        <f>+IF(E210="","",VLOOKUP(E210,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M210" s="15"/>
-    </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A211" s="13"/>
-      <c r="B211" s="13"/>
-      <c r="C211" s="17"/>
-      <c r="E211" s="88"/>
-      <c r="F211" s="6" t="e">
-        <f>+VLOOKUP(E211,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G211" s="14"/>
-      <c r="H211" s="14"/>
-      <c r="I211" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J211" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K211" t="str">
-        <f>+IF(E211="","",VLOOKUP(E211,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L211" t="str">
-        <f>+IF(E211="","",VLOOKUP(E211,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M211" s="15"/>
-    </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A212" s="13"/>
-      <c r="B212" s="13"/>
-      <c r="C212" s="17"/>
-      <c r="E212" s="88"/>
-      <c r="F212" s="6" t="e">
-        <f>+VLOOKUP(E212,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G212" s="14"/>
-      <c r="H212" s="14"/>
-      <c r="I212" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J212" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K212" t="str">
-        <f>+IF(E212="","",VLOOKUP(E212,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L212" t="str">
-        <f>+IF(E212="","",VLOOKUP(E212,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M212" s="15"/>
-    </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A213" s="13"/>
-      <c r="B213" s="13"/>
-      <c r="C213" s="17"/>
-      <c r="E213" s="88"/>
-      <c r="F213" s="6" t="e">
-        <f>+VLOOKUP(E213,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G213" s="14"/>
-      <c r="H213" s="14"/>
-      <c r="I213" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J213" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K213" t="str">
-        <f>+IF(E213="","",VLOOKUP(E213,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L213" t="str">
-        <f>+IF(E213="","",VLOOKUP(E213,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M213" s="15"/>
-    </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A214" s="13"/>
-      <c r="B214" s="13"/>
-      <c r="C214" s="17"/>
-      <c r="E214" s="88"/>
-      <c r="F214" s="6" t="e">
-        <f>+VLOOKUP(E214,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G214" s="14"/>
-      <c r="H214" s="14"/>
-      <c r="I214" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J214" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K214" t="str">
-        <f>+IF(E214="","",VLOOKUP(E214,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L214" t="str">
-        <f>+IF(E214="","",VLOOKUP(E214,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M214" s="15"/>
-    </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A215" s="13"/>
-      <c r="B215" s="13"/>
-      <c r="C215" s="17"/>
-      <c r="E215" s="88"/>
-      <c r="F215" s="6" t="e">
-        <f>+VLOOKUP(E215,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G215" s="14"/>
-      <c r="H215" s="14"/>
-      <c r="I215" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J215" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K215" t="str">
-        <f>+IF(E215="","",VLOOKUP(E215,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L215" t="str">
-        <f>+IF(E215="","",VLOOKUP(E215,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M215" s="15"/>
-    </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A216" s="13"/>
-      <c r="B216" s="13"/>
-      <c r="C216" s="17"/>
-      <c r="E216" s="88"/>
-      <c r="F216" s="6" t="e">
-        <f>+VLOOKUP(E216,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G216" s="14"/>
-      <c r="H216" s="14"/>
-      <c r="I216" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J216" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K216" t="str">
-        <f>+IF(E216="","",VLOOKUP(E216,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L216" t="str">
-        <f>+IF(E216="","",VLOOKUP(E216,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M216" s="15"/>
-    </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A217" s="13"/>
-      <c r="B217" s="13"/>
-      <c r="C217" s="17"/>
-      <c r="E217" s="88"/>
-      <c r="F217" s="6" t="e">
-        <f>+VLOOKUP(E217,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G217" s="14"/>
-      <c r="H217" s="14"/>
-      <c r="I217" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J217" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K217" t="str">
-        <f>+IF(E217="","",VLOOKUP(E217,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L217" t="str">
-        <f>+IF(E217="","",VLOOKUP(E217,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M217" s="15"/>
-    </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A218" s="13"/>
-      <c r="B218" s="13"/>
-      <c r="C218" s="17"/>
-      <c r="E218" s="88"/>
-      <c r="F218" s="6" t="e">
-        <f>+VLOOKUP(E218,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G218" s="14"/>
-      <c r="H218" s="14"/>
-      <c r="I218" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J218" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K218" t="str">
-        <f>+IF(E218="","",VLOOKUP(E218,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L218" t="str">
-        <f>+IF(E218="","",VLOOKUP(E218,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M218" s="15"/>
-    </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A219" s="13"/>
-      <c r="B219" s="13"/>
-      <c r="C219" s="17"/>
-      <c r="E219" s="88"/>
-      <c r="F219" s="6" t="e">
-        <f>+VLOOKUP(E219,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G219" s="14"/>
-      <c r="H219" s="14"/>
-      <c r="I219" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J219" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K219" t="str">
-        <f>+IF(E219="","",VLOOKUP(E219,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L219" t="str">
-        <f>+IF(E219="","",VLOOKUP(E219,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M219" s="15"/>
-    </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A220" s="13"/>
-      <c r="B220" s="13"/>
-      <c r="C220" s="17"/>
-      <c r="E220" s="88"/>
-      <c r="F220" s="6" t="e">
-        <f>+VLOOKUP(E220,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G220" s="14"/>
-      <c r="H220" s="14"/>
-      <c r="I220" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J220" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K220" t="str">
-        <f>+IF(E220="","",VLOOKUP(E220,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L220" t="str">
-        <f>+IF(E220="","",VLOOKUP(E220,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M220" s="15"/>
-    </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A221" s="13"/>
-      <c r="B221" s="13"/>
-      <c r="C221" s="17"/>
-      <c r="E221" s="88"/>
-      <c r="F221" s="6" t="e">
-        <f>+VLOOKUP(E221,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G221" s="14"/>
-      <c r="H221" s="14"/>
-      <c r="I221" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J221" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K221" t="str">
-        <f>+IF(E221="","",VLOOKUP(E221,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L221" t="str">
-        <f>+IF(E221="","",VLOOKUP(E221,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M221" s="15"/>
-    </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A222" s="13"/>
-      <c r="B222" s="13"/>
-      <c r="C222" s="17"/>
-      <c r="E222" s="88"/>
-      <c r="F222" s="6" t="e">
-        <f>+VLOOKUP(E222,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G222" s="14"/>
-      <c r="H222" s="14"/>
-      <c r="I222" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J222" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K222" t="str">
-        <f>+IF(E222="","",VLOOKUP(E222,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L222" t="str">
-        <f>+IF(E222="","",VLOOKUP(E222,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M222" s="15"/>
-    </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A223" s="13"/>
-      <c r="B223" s="13"/>
-      <c r="C223" s="17"/>
-      <c r="E223" s="88"/>
-      <c r="F223" s="6" t="e">
-        <f>+VLOOKUP(E223,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G223" s="14"/>
-      <c r="H223" s="14"/>
-      <c r="I223" s="16">
-        <v>46276</v>
-      </c>
-      <c r="J223" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K223" t="str">
-        <f>+IF(E223="","",VLOOKUP(E223,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L223" t="str">
-        <f>+IF(E223="","",VLOOKUP(E223,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M223" s="15"/>
-    </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A224" s="13"/>
-      <c r="B224" s="13"/>
-      <c r="C224" s="17"/>
-      <c r="E224" s="88"/>
-      <c r="F224" s="6" t="e">
-        <f>+VLOOKUP(E224,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G224" s="14"/>
-      <c r="H224" s="14"/>
-      <c r="I224" s="16">
-        <v>46276</v>
-      </c>
-      <c r="J224" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K224" t="str">
-        <f>+IF(E224="","",VLOOKUP(E224,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L224" t="str">
-        <f>+IF(E224="","",VLOOKUP(E224,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M224" s="15"/>
-    </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A225" s="13"/>
-      <c r="B225" s="13"/>
-      <c r="C225" s="17"/>
-      <c r="E225" s="88"/>
-      <c r="F225" s="6" t="e">
-        <f>+VLOOKUP(E225,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G225" s="14"/>
-      <c r="H225" s="14"/>
-      <c r="I225" s="16">
-        <v>46276</v>
-      </c>
-      <c r="J225" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K225" t="str">
-        <f>+IF(E225="","",VLOOKUP(E225,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L225" t="str">
-        <f>+IF(E225="","",VLOOKUP(E225,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M225" s="15"/>
-    </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A226" s="13"/>
-      <c r="B226" s="13"/>
-      <c r="C226" s="17"/>
-      <c r="E226" s="88"/>
-      <c r="F226" s="6" t="e">
-        <f>+VLOOKUP(E226,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G226" s="14"/>
-      <c r="H226" s="14"/>
-      <c r="I226" s="16">
-        <v>46276</v>
-      </c>
-      <c r="J226" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K226" t="str">
-        <f>+IF(E226="","",VLOOKUP(E226,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L226" t="str">
-        <f>+IF(E226="","",VLOOKUP(E226,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M226" s="15"/>
-    </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A227" s="13"/>
-      <c r="B227" s="13"/>
-      <c r="C227" s="17"/>
-      <c r="E227" s="88"/>
-      <c r="F227" s="6" t="e">
-        <f>+VLOOKUP(E227,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G227" s="14"/>
-      <c r="H227" s="14"/>
-      <c r="I227" s="16">
-        <v>46276</v>
-      </c>
-      <c r="J227" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K227" t="str">
-        <f>+IF(E227="","",VLOOKUP(E227,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L227" t="str">
-        <f>+IF(E227="","",VLOOKUP(E227,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M227" s="15"/>
-    </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A228" s="13"/>
-      <c r="B228" s="13"/>
-      <c r="C228" s="17"/>
-      <c r="E228" s="88"/>
-      <c r="F228" s="6" t="e">
-        <f>+VLOOKUP(E228,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G228" s="14"/>
-      <c r="H228" s="14"/>
-      <c r="I228" s="16">
-        <v>46276</v>
-      </c>
-      <c r="J228" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K228" t="str">
-        <f>+IF(E228="","",VLOOKUP(E228,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L228" t="str">
-        <f>+IF(E228="","",VLOOKUP(E228,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M228" s="15"/>
-    </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A229" s="13"/>
-      <c r="B229" s="13"/>
-      <c r="C229" s="17"/>
-      <c r="E229" s="88"/>
-      <c r="F229" s="6" t="e">
-        <f>+VLOOKUP(E229,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G229" s="14"/>
-      <c r="H229" s="14"/>
-      <c r="I229" s="16">
-        <v>46276</v>
-      </c>
-      <c r="J229" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K229" t="str">
-        <f>+IF(E229="","",VLOOKUP(E229,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L229" t="str">
-        <f>+IF(E229="","",VLOOKUP(E229,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M229" s="15"/>
-    </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A230" s="13"/>
-      <c r="B230" s="13"/>
-      <c r="C230" s="17"/>
-      <c r="E230" s="88"/>
-      <c r="F230" s="6" t="e">
-        <f>+VLOOKUP(E230,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G230" s="14"/>
-      <c r="H230" s="14"/>
-      <c r="I230" s="16">
-        <v>46276</v>
-      </c>
-      <c r="J230" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K230" t="str">
-        <f>+IF(E230="","",VLOOKUP(E230,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L230" t="str">
-        <f>+IF(E230="","",VLOOKUP(E230,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M230" s="15"/>
-    </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A231" s="13"/>
-      <c r="B231" s="13"/>
-      <c r="C231" s="17"/>
-      <c r="E231" s="88"/>
-      <c r="F231" s="6" t="e">
-        <f>+VLOOKUP(E231,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G231" s="14"/>
-      <c r="H231" s="14"/>
-      <c r="I231" s="16">
-        <v>46276</v>
-      </c>
-      <c r="J231" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K231" t="str">
-        <f>+IF(E231="","",VLOOKUP(E231,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L231" t="str">
-        <f>+IF(E231="","",VLOOKUP(E231,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M231" s="15"/>
-    </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A232" s="13"/>
-      <c r="B232" s="13"/>
-      <c r="C232" s="17"/>
-      <c r="E232" s="88"/>
-      <c r="F232" s="6" t="e">
-        <f>+VLOOKUP(E232,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G232" s="14"/>
-      <c r="H232" s="14"/>
-      <c r="I232" s="16">
-        <v>46276</v>
-      </c>
-      <c r="J232" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K232" t="str">
-        <f>+IF(E232="","",VLOOKUP(E232,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L232" t="str">
-        <f>+IF(E232="","",VLOOKUP(E232,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M232" s="15"/>
-    </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A233" s="13"/>
-      <c r="B233" s="13"/>
-      <c r="C233" s="17"/>
-      <c r="E233" s="88"/>
-      <c r="F233" s="6" t="e">
-        <f>+VLOOKUP(E233,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G233" s="14"/>
-      <c r="H233" s="14"/>
-      <c r="I233" s="16">
-        <v>46276</v>
-      </c>
-      <c r="J233" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K233" t="str">
-        <f>+IF(E233="","",VLOOKUP(E233,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L233" t="str">
-        <f>+IF(E233="","",VLOOKUP(E233,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M233" s="15"/>
-    </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A234" s="13"/>
-      <c r="B234" s="13"/>
-      <c r="C234" s="17"/>
-      <c r="E234" s="88"/>
-      <c r="F234" s="6" t="e">
-        <f>+VLOOKUP(E234,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G234" s="14"/>
-      <c r="H234" s="14"/>
-      <c r="I234" s="16">
-        <v>46276</v>
-      </c>
-      <c r="J234" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K234" t="str">
-        <f>+IF(E234="","",VLOOKUP(E234,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L234" t="str">
-        <f>+IF(E234="","",VLOOKUP(E234,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M234" s="15"/>
-    </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A235" s="13"/>
-      <c r="B235" s="13"/>
-      <c r="C235" s="17"/>
-      <c r="E235" s="88"/>
-      <c r="F235" s="6" t="e">
-        <f>+VLOOKUP(E235,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G235" s="14"/>
-      <c r="H235" s="14"/>
-      <c r="I235" s="16">
-        <v>46276</v>
-      </c>
-      <c r="J235" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K235" t="str">
-        <f>+IF(E235="","",VLOOKUP(E235,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L235" t="str">
-        <f>+IF(E235="","",VLOOKUP(E235,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M235" s="15"/>
-    </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A236" s="13"/>
-      <c r="B236" s="13"/>
-      <c r="C236" s="17"/>
-      <c r="E236" s="88"/>
-      <c r="F236" s="6" t="e">
-        <f>+VLOOKUP(E236,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G236" s="14"/>
-      <c r="H236" s="14"/>
-      <c r="I236" s="16">
-        <v>46277</v>
-      </c>
-      <c r="J236" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K236" t="str">
-        <f>+IF(E236="","",VLOOKUP(E236,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L236" t="str">
-        <f>+IF(E236="","",VLOOKUP(E236,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M236" s="15"/>
-    </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A237" s="13"/>
-      <c r="B237" s="13"/>
-      <c r="C237" s="17"/>
-      <c r="E237" s="88"/>
-      <c r="F237" s="6" t="e">
-        <f>+VLOOKUP(E237,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G237" s="14"/>
-      <c r="H237" s="14"/>
-      <c r="I237" s="16">
-        <v>46277</v>
-      </c>
-      <c r="J237" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K237" t="str">
-        <f>+IF(E237="","",VLOOKUP(E237,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L237" t="str">
-        <f>+IF(E237="","",VLOOKUP(E237,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M237" s="15"/>
-    </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A238" s="13"/>
-      <c r="B238" s="13"/>
-      <c r="C238" s="17"/>
-      <c r="E238" s="88"/>
-      <c r="F238" s="6" t="e">
-        <f>+VLOOKUP(E238,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G238" s="14"/>
-      <c r="H238" s="14"/>
-      <c r="I238" s="16">
-        <v>46277</v>
-      </c>
-      <c r="J238" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K238" t="str">
-        <f>+IF(E238="","",VLOOKUP(E238,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L238" t="str">
-        <f>+IF(E238="","",VLOOKUP(E238,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M238" s="15"/>
-    </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A239" s="13"/>
-      <c r="B239" s="13"/>
-      <c r="C239" s="17"/>
-      <c r="E239" s="88"/>
-      <c r="F239" s="6" t="e">
-        <f>+VLOOKUP(E239,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G239" s="14"/>
-      <c r="H239" s="14"/>
-      <c r="I239" s="16">
-        <v>46277</v>
-      </c>
-      <c r="J239" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K239" t="str">
-        <f>+IF(E239="","",VLOOKUP(E239,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L239" t="str">
-        <f>+IF(E239="","",VLOOKUP(E239,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M239" s="15"/>
-    </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A240" s="13"/>
-      <c r="B240" s="13"/>
-      <c r="C240" s="17"/>
-      <c r="E240" s="88"/>
-      <c r="F240" s="6" t="e">
-        <f>+VLOOKUP(E240,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G240" s="14"/>
-      <c r="H240" s="14"/>
-      <c r="I240" s="16">
-        <v>46277</v>
-      </c>
-      <c r="J240" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K240" t="str">
-        <f>+IF(E240="","",VLOOKUP(E240,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L240" t="str">
-        <f>+IF(E240="","",VLOOKUP(E240,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M240" s="15"/>
-    </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A241" s="13"/>
-      <c r="B241" s="13"/>
-      <c r="C241" s="17"/>
-      <c r="E241" s="88"/>
-      <c r="F241" s="6" t="e">
-        <f>+VLOOKUP(E241,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G241" s="14"/>
-      <c r="H241" s="14"/>
-      <c r="I241" s="16">
-        <v>46277</v>
-      </c>
-      <c r="J241" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K241" t="str">
-        <f>+IF(E241="","",VLOOKUP(E241,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L241" t="str">
-        <f>+IF(E241="","",VLOOKUP(E241,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M241" s="15"/>
-    </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A242" s="13"/>
-      <c r="B242" s="13"/>
-      <c r="C242" s="17"/>
-      <c r="E242" s="88"/>
-      <c r="F242" s="6" t="e">
-        <f>+VLOOKUP(E242,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G242" s="14"/>
-      <c r="H242" s="14"/>
-      <c r="I242" s="16">
-        <v>46277</v>
-      </c>
-      <c r="J242" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K242" t="str">
-        <f>+IF(E242="","",VLOOKUP(E242,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L242" t="str">
-        <f>+IF(E242="","",VLOOKUP(E242,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M242" s="15"/>
-    </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A243" s="13"/>
-      <c r="B243" s="13"/>
-      <c r="C243" s="17"/>
-      <c r="E243" s="88"/>
-      <c r="F243" s="6" t="e">
-        <f>+VLOOKUP(E243,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G243" s="14"/>
-      <c r="H243" s="14"/>
-      <c r="I243" s="16">
-        <v>46277</v>
-      </c>
-      <c r="J243" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K243" t="str">
-        <f>+IF(E243="","",VLOOKUP(E243,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L243" t="str">
-        <f>+IF(E243="","",VLOOKUP(E243,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M243" s="15"/>
-    </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A244" s="13"/>
-      <c r="B244" s="13"/>
-      <c r="C244" s="17"/>
-      <c r="E244" s="88"/>
-      <c r="F244" s="6" t="e">
-        <f>+VLOOKUP(E244,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G244" s="14"/>
-      <c r="H244" s="14"/>
-      <c r="I244" s="16">
-        <v>46277</v>
-      </c>
-      <c r="J244" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K244" t="str">
-        <f>+IF(E244="","",VLOOKUP(E244,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L244" t="str">
-        <f>+IF(E244="","",VLOOKUP(E244,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M244" s="15"/>
-    </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A245" s="13"/>
-      <c r="B245" s="13"/>
-      <c r="C245" s="17"/>
-      <c r="E245" s="88"/>
-      <c r="F245" s="6" t="e">
-        <f>+VLOOKUP(E245,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G245" s="14"/>
-      <c r="H245" s="14"/>
-      <c r="I245" s="16">
-        <v>46277</v>
-      </c>
-      <c r="J245" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K245" t="str">
-        <f>+IF(E245="","",VLOOKUP(E245,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L245" t="str">
-        <f>+IF(E245="","",VLOOKUP(E245,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M245" s="15"/>
-    </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A246" s="13"/>
-      <c r="B246" s="13"/>
-      <c r="C246" s="17"/>
-      <c r="E246" s="88"/>
-      <c r="F246" s="6" t="e">
-        <f>+VLOOKUP(E246,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G246" s="14"/>
-      <c r="H246" s="14"/>
-      <c r="I246" s="16">
-        <v>46277</v>
-      </c>
-      <c r="J246" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K246" t="str">
-        <f>+IF(E246="","",VLOOKUP(E246,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L246" t="str">
-        <f>+IF(E246="","",VLOOKUP(E246,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M246" s="15"/>
-    </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A247" s="13"/>
-      <c r="B247" s="13"/>
-      <c r="C247" s="17"/>
-      <c r="E247" s="88"/>
-      <c r="F247" s="6" t="e">
-        <f>+VLOOKUP(E247,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G247" s="14"/>
-      <c r="H247" s="14"/>
-      <c r="I247" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J247" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K247" t="str">
-        <f>+IF(E247="","",VLOOKUP(E247,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L247" t="str">
-        <f>+IF(E247="","",VLOOKUP(E247,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M247" s="15"/>
-    </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A248" s="13"/>
-      <c r="B248" s="13"/>
-      <c r="C248" s="17"/>
-      <c r="E248" s="88"/>
-      <c r="F248" s="6" t="e">
-        <f>+VLOOKUP(E248,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G248" s="14"/>
-      <c r="H248" s="14"/>
-      <c r="I248" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J248" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K248" t="str">
-        <f>+IF(E248="","",VLOOKUP(E248,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L248" t="str">
-        <f>+IF(E248="","",VLOOKUP(E248,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M248" s="15"/>
-    </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A249" s="13"/>
-      <c r="B249" s="13"/>
-      <c r="C249" s="17"/>
-      <c r="E249" s="88"/>
-      <c r="F249" s="6" t="e">
-        <f>+VLOOKUP(E249,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G249" s="14"/>
-      <c r="H249" s="14"/>
-      <c r="I249" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J249" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K249" t="str">
-        <f>+IF(E249="","",VLOOKUP(E249,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L249" t="str">
-        <f>+IF(E249="","",VLOOKUP(E249,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M249" s="15"/>
-    </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A250" s="13"/>
-      <c r="B250" s="13"/>
-      <c r="C250" s="17"/>
-      <c r="E250" s="88"/>
-      <c r="F250" s="6" t="e">
-        <f>+VLOOKUP(E250,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G250" s="14"/>
-      <c r="H250" s="14"/>
-      <c r="I250" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J250" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K250" t="str">
-        <f>+IF(E250="","",VLOOKUP(E250,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L250" t="str">
-        <f>+IF(E250="","",VLOOKUP(E250,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M250" s="15"/>
-    </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A251" s="13"/>
-      <c r="B251" s="13"/>
-      <c r="C251" s="17"/>
-      <c r="E251" s="88"/>
-      <c r="F251" s="6" t="e">
-        <f>+VLOOKUP(E251,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G251" s="14"/>
-      <c r="H251" s="14"/>
-      <c r="I251" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J251" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K251" t="str">
-        <f>+IF(E251="","",VLOOKUP(E251,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L251" t="str">
-        <f>+IF(E251="","",VLOOKUP(E251,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M251" s="15"/>
-    </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A252" s="13"/>
-      <c r="B252" s="13"/>
-      <c r="C252" s="17"/>
-      <c r="E252" s="88"/>
-      <c r="F252" s="6" t="e">
-        <f>+VLOOKUP(E252,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G252" s="14"/>
-      <c r="H252" s="14"/>
-      <c r="I252" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J252" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K252" t="str">
-        <f>+IF(E252="","",VLOOKUP(E252,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L252" t="str">
-        <f>+IF(E252="","",VLOOKUP(E252,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M252" s="15"/>
-    </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A253" s="13"/>
-      <c r="B253" s="13"/>
-      <c r="C253" s="17"/>
-      <c r="E253" s="88"/>
-      <c r="F253" s="6" t="e">
-        <f>+VLOOKUP(E253,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G253" s="14"/>
-      <c r="H253" s="14"/>
-      <c r="I253" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J253" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K253" t="str">
-        <f>+IF(E253="","",VLOOKUP(E253,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L253" t="str">
-        <f>+IF(E253="","",VLOOKUP(E253,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M253" s="15"/>
-    </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A254" s="13"/>
-      <c r="B254" s="13"/>
-      <c r="C254" s="17"/>
-      <c r="E254" s="88"/>
-      <c r="F254" s="6" t="e">
-        <f>+VLOOKUP(E254,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G254" s="14"/>
-      <c r="H254" s="14"/>
-      <c r="I254" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J254" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K254" t="str">
-        <f>+IF(E254="","",VLOOKUP(E254,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L254" t="str">
-        <f>+IF(E254="","",VLOOKUP(E254,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M254" s="15"/>
-    </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A255" s="13"/>
-      <c r="B255" s="13"/>
-      <c r="C255" s="17"/>
-      <c r="E255" s="88"/>
-      <c r="F255" s="6" t="e">
-        <f>+VLOOKUP(E255,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G255" s="14"/>
-      <c r="H255" s="14"/>
-      <c r="I255" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J255" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K255" t="str">
-        <f>+IF(E255="","",VLOOKUP(E255,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L255" t="str">
-        <f>+IF(E255="","",VLOOKUP(E255,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M255" s="15"/>
-    </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A256" s="13"/>
-      <c r="B256" s="13"/>
-      <c r="C256" s="17"/>
-      <c r="E256" s="88"/>
-      <c r="F256" s="6" t="e">
-        <f>+VLOOKUP(E256,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G256" s="14"/>
-      <c r="H256" s="14"/>
-      <c r="I256" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J256" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K256" t="str">
-        <f>+IF(E256="","",VLOOKUP(E256,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L256" t="str">
-        <f>+IF(E256="","",VLOOKUP(E256,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M256" s="15"/>
-    </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A257" s="13"/>
-      <c r="B257" s="13"/>
-      <c r="C257" s="17"/>
-      <c r="E257" s="88"/>
-      <c r="F257" s="6" t="e">
-        <f>+VLOOKUP(E257,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G257" s="14"/>
-      <c r="H257" s="14"/>
-      <c r="I257" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J257" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K257" t="str">
-        <f>+IF(E257="","",VLOOKUP(E257,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L257" t="str">
-        <f>+IF(E257="","",VLOOKUP(E257,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M257" s="15"/>
-    </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A258" s="13"/>
-      <c r="B258" s="13"/>
-      <c r="C258" s="17"/>
-      <c r="E258" s="88"/>
-      <c r="F258" s="6" t="e">
-        <f>+VLOOKUP(E258,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G258" s="14"/>
-      <c r="H258" s="14"/>
-      <c r="I258" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J258" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K258" t="str">
-        <f>+IF(E258="","",VLOOKUP(E258,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L258" t="str">
-        <f>+IF(E258="","",VLOOKUP(E258,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M258" s="15"/>
-    </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A259" s="13"/>
-      <c r="B259" s="13"/>
-      <c r="C259" s="17"/>
-      <c r="E259" s="88"/>
-      <c r="F259" s="6" t="e">
-        <f>+VLOOKUP(E259,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G259" s="14"/>
-      <c r="H259" s="14"/>
-      <c r="I259" s="16">
-        <v>46272</v>
-      </c>
-      <c r="J259" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K259" t="str">
-        <f>+IF(E259="","",VLOOKUP(E259,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L259" t="str">
-        <f>+IF(E259="","",VLOOKUP(E259,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M259" s="15"/>
-    </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A260" s="13"/>
-      <c r="B260" s="13"/>
-      <c r="C260" s="17"/>
-      <c r="E260" s="88"/>
-      <c r="F260" s="6" t="e">
-        <f>+VLOOKUP(E260,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G260" s="14"/>
-      <c r="H260" s="14"/>
-      <c r="I260" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J260" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K260" t="str">
-        <f>+IF(E260="","",VLOOKUP(E260,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L260" t="str">
-        <f>+IF(E260="","",VLOOKUP(E260,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M260" s="15"/>
-    </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A261" s="13"/>
-      <c r="B261" s="13"/>
-      <c r="C261" s="17"/>
-      <c r="E261" s="88"/>
-      <c r="F261" s="6" t="e">
-        <f>+VLOOKUP(E261,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G261" s="14"/>
-      <c r="H261" s="14"/>
-      <c r="I261" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J261" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K261" t="str">
-        <f>+IF(E261="","",VLOOKUP(E261,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L261" t="str">
-        <f>+IF(E261="","",VLOOKUP(E261,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M261" s="15"/>
-    </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A262" s="13"/>
-      <c r="B262" s="13"/>
-      <c r="C262" s="17"/>
-      <c r="E262" s="88"/>
-      <c r="F262" s="6" t="e">
-        <f>+VLOOKUP(E262,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G262" s="14"/>
-      <c r="H262" s="14"/>
-      <c r="I262" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J262" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K262" t="str">
-        <f>+IF(E262="","",VLOOKUP(E262,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L262" t="str">
-        <f>+IF(E262="","",VLOOKUP(E262,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M262" s="15"/>
-    </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A263" s="13"/>
-      <c r="B263" s="13"/>
-      <c r="C263" s="17"/>
-      <c r="E263" s="88"/>
-      <c r="F263" s="6" t="e">
-        <f>+VLOOKUP(E263,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G263" s="14"/>
-      <c r="H263" s="14"/>
-      <c r="I263" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J263" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K263" t="str">
-        <f>+IF(E263="","",VLOOKUP(E263,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L263" t="str">
-        <f>+IF(E263="","",VLOOKUP(E263,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M263" s="15"/>
-    </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A264" s="13"/>
-      <c r="B264" s="13"/>
-      <c r="C264" s="17"/>
-      <c r="E264" s="88"/>
-      <c r="F264" s="6" t="e">
-        <f>+VLOOKUP(E264,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G264" s="14"/>
-      <c r="H264" s="14"/>
-      <c r="I264" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J264" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K264" t="str">
-        <f>+IF(E264="","",VLOOKUP(E264,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L264" t="str">
-        <f>+IF(E264="","",VLOOKUP(E264,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M264" s="15"/>
-    </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A265" s="13"/>
-      <c r="B265" s="13"/>
-      <c r="C265" s="17"/>
-      <c r="E265" s="88"/>
-      <c r="F265" s="6" t="e">
-        <f>+VLOOKUP(E265,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G265" s="14"/>
-      <c r="H265" s="14"/>
-      <c r="I265" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J265" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K265" t="str">
-        <f>+IF(E265="","",VLOOKUP(E265,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L265" t="str">
-        <f>+IF(E265="","",VLOOKUP(E265,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M265" s="15"/>
-    </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A266" s="13"/>
-      <c r="B266" s="13"/>
-      <c r="C266" s="17"/>
-      <c r="E266" s="88"/>
-      <c r="F266" s="6" t="e">
-        <f>+VLOOKUP(E266,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G266" s="14"/>
-      <c r="H266" s="14"/>
-      <c r="I266" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J266" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K266" t="str">
-        <f>+IF(E266="","",VLOOKUP(E266,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L266" t="str">
-        <f>+IF(E266="","",VLOOKUP(E266,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M266" s="15"/>
-    </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A267" s="13"/>
-      <c r="B267" s="13"/>
-      <c r="C267" s="17"/>
-      <c r="E267" s="88"/>
-      <c r="F267" s="6" t="e">
-        <f>+VLOOKUP(E267,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G267" s="14"/>
-      <c r="H267" s="14"/>
-      <c r="I267" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J267" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K267" t="str">
-        <f>+IF(E267="","",VLOOKUP(E267,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L267" t="str">
-        <f>+IF(E267="","",VLOOKUP(E267,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M267" s="15"/>
-    </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A268" s="13"/>
-      <c r="B268" s="13"/>
-      <c r="C268" s="17"/>
-      <c r="E268" s="88"/>
-      <c r="F268" s="6" t="e">
-        <f>+VLOOKUP(E268,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G268" s="14"/>
-      <c r="H268" s="14"/>
-      <c r="I268" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J268" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K268" t="str">
-        <f>+IF(E268="","",VLOOKUP(E268,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L268" t="str">
-        <f>+IF(E268="","",VLOOKUP(E268,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M268" s="15"/>
-    </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A269" s="13"/>
-      <c r="B269" s="13"/>
-      <c r="C269" s="17"/>
-      <c r="E269" s="88"/>
-      <c r="F269" s="6" t="e">
-        <f>+VLOOKUP(E269,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G269" s="14"/>
-      <c r="H269" s="14"/>
-      <c r="I269" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J269" s="12">
-        <f t="shared" si="4"/>
-        <v>37</v>
-      </c>
-      <c r="K269" t="str">
-        <f>+IF(E269="","",VLOOKUP(E269,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L269" t="str">
-        <f>+IF(E269="","",VLOOKUP(E269,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M269" s="15"/>
-    </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A270" s="13"/>
-      <c r="B270" s="13"/>
-      <c r="C270" s="17"/>
-      <c r="E270" s="88"/>
-      <c r="F270" s="6" t="e">
-        <f>+VLOOKUP(E270,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G270" s="14"/>
-      <c r="H270" s="14"/>
-      <c r="I270" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J270" s="12">
-        <f t="shared" ref="J270:J313" si="5">+WEEKNUM(I270)</f>
-        <v>37</v>
-      </c>
-      <c r="K270" t="str">
-        <f>+IF(E270="","",VLOOKUP(E270,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L270" t="str">
-        <f>+IF(E270="","",VLOOKUP(E270,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M270" s="15"/>
-    </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A271" s="13"/>
-      <c r="B271" s="13"/>
-      <c r="C271" s="17"/>
-      <c r="E271" s="88"/>
-      <c r="F271" s="6" t="e">
-        <f>+VLOOKUP(E271,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G271" s="14"/>
-      <c r="H271" s="14"/>
-      <c r="I271" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J271" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K271" t="str">
-        <f>+IF(E271="","",VLOOKUP(E271,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L271" t="str">
-        <f>+IF(E271="","",VLOOKUP(E271,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M271" s="15"/>
-    </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A272" s="13"/>
-      <c r="B272" s="13"/>
-      <c r="C272" s="17"/>
-      <c r="E272" s="88"/>
-      <c r="F272" s="6" t="e">
-        <f>+VLOOKUP(E272,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G272" s="14"/>
-      <c r="H272" s="14"/>
-      <c r="I272" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J272" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K272" t="str">
-        <f>+IF(E272="","",VLOOKUP(E272,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L272" t="str">
-        <f>+IF(E272="","",VLOOKUP(E272,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M272" s="15"/>
-    </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A273" s="13"/>
-      <c r="B273" s="13"/>
-      <c r="C273" s="17"/>
-      <c r="E273" s="88"/>
-      <c r="F273" s="6" t="e">
-        <f>+VLOOKUP(E273,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G273" s="14"/>
-      <c r="H273" s="14"/>
-      <c r="I273" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J273" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K273" t="str">
-        <f>+IF(E273="","",VLOOKUP(E273,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L273" t="str">
-        <f>+IF(E273="","",VLOOKUP(E273,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M273" s="15"/>
-    </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A274" s="13"/>
-      <c r="B274" s="13"/>
-      <c r="C274" s="17"/>
-      <c r="E274" s="88"/>
-      <c r="F274" s="6" t="e">
-        <f>+VLOOKUP(E274,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G274" s="14"/>
-      <c r="H274" s="14"/>
-      <c r="I274" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J274" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K274" t="str">
-        <f>+IF(E274="","",VLOOKUP(E274,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L274" t="str">
-        <f>+IF(E274="","",VLOOKUP(E274,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M274" s="15"/>
-    </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A275" s="13"/>
-      <c r="B275" s="13"/>
-      <c r="C275" s="17"/>
-      <c r="E275" s="88"/>
-      <c r="F275" s="6" t="e">
-        <f>+VLOOKUP(E275,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G275" s="14"/>
-      <c r="H275" s="14"/>
-      <c r="I275" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J275" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K275" t="str">
-        <f>+IF(E275="","",VLOOKUP(E275,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L275" t="str">
-        <f>+IF(E275="","",VLOOKUP(E275,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M275" s="15"/>
-    </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A276" s="13"/>
-      <c r="B276" s="13"/>
-      <c r="C276" s="17"/>
-      <c r="E276" s="88"/>
-      <c r="F276" s="6" t="e">
-        <f>+VLOOKUP(E276,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G276" s="14"/>
-      <c r="H276" s="14"/>
-      <c r="I276" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J276" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K276" t="str">
-        <f>+IF(E276="","",VLOOKUP(E276,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L276" t="str">
-        <f>+IF(E276="","",VLOOKUP(E276,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M276" s="15"/>
-    </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A277" s="13"/>
-      <c r="B277" s="13"/>
-      <c r="C277" s="17"/>
-      <c r="E277" s="88"/>
-      <c r="F277" s="6" t="e">
-        <f>+VLOOKUP(E277,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G277" s="14"/>
-      <c r="H277" s="14"/>
-      <c r="I277" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J277" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K277" t="str">
-        <f>+IF(E277="","",VLOOKUP(E277,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L277" t="str">
-        <f>+IF(E277="","",VLOOKUP(E277,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M277" s="15"/>
-    </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A278" s="13"/>
-      <c r="B278" s="13"/>
-      <c r="C278" s="17"/>
-      <c r="E278" s="88"/>
-      <c r="F278" s="6" t="e">
-        <f>+VLOOKUP(E278,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G278" s="14"/>
-      <c r="H278" s="14"/>
-      <c r="I278" s="16">
-        <v>46273</v>
-      </c>
-      <c r="J278" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K278" t="str">
-        <f>+IF(E278="","",VLOOKUP(E278,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L278" t="str">
-        <f>+IF(E278="","",VLOOKUP(E278,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M278" s="15"/>
-    </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A279" s="13"/>
-      <c r="B279" s="13"/>
-      <c r="C279" s="17"/>
-      <c r="E279" s="88"/>
-      <c r="F279" s="6" t="e">
-        <f>+VLOOKUP(E279,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G279" s="14"/>
-      <c r="H279" s="14"/>
-      <c r="I279" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J279" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K279" t="str">
-        <f>+IF(E279="","",VLOOKUP(E279,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L279" t="str">
-        <f>+IF(E279="","",VLOOKUP(E279,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M279" s="15"/>
-    </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A280" s="13"/>
-      <c r="B280" s="13"/>
-      <c r="C280" s="17"/>
-      <c r="E280" s="88"/>
-      <c r="F280" s="6" t="e">
-        <f>+VLOOKUP(E280,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G280" s="14"/>
-      <c r="H280" s="14"/>
-      <c r="I280" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J280" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K280" t="str">
-        <f>+IF(E280="","",VLOOKUP(E280,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L280" t="str">
-        <f>+IF(E280="","",VLOOKUP(E280,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M280" s="15"/>
-    </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A281" s="13"/>
-      <c r="B281" s="13"/>
-      <c r="C281" s="17"/>
-      <c r="E281" s="88"/>
-      <c r="F281" s="6" t="e">
-        <f>+VLOOKUP(E281,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G281" s="14"/>
-      <c r="H281" s="14"/>
-      <c r="I281" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J281" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K281" t="str">
-        <f>+IF(E281="","",VLOOKUP(E281,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L281" t="str">
-        <f>+IF(E281="","",VLOOKUP(E281,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M281" s="15"/>
-    </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A282" s="13"/>
-      <c r="B282" s="13"/>
-      <c r="C282" s="17"/>
-      <c r="E282" s="88"/>
-      <c r="F282" s="6" t="e">
-        <f>+VLOOKUP(E282,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G282" s="14"/>
-      <c r="H282" s="14"/>
-      <c r="I282" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J282" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K282" t="str">
-        <f>+IF(E282="","",VLOOKUP(E282,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L282" t="str">
-        <f>+IF(E282="","",VLOOKUP(E282,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M282" s="15"/>
-    </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A283" s="13"/>
-      <c r="B283" s="13"/>
-      <c r="C283" s="17"/>
-      <c r="E283" s="88"/>
-      <c r="F283" s="6" t="e">
-        <f>+VLOOKUP(E283,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G283" s="14"/>
-      <c r="H283" s="14"/>
-      <c r="I283" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J283" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K283" t="str">
-        <f>+IF(E283="","",VLOOKUP(E283,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L283" t="str">
-        <f>+IF(E283="","",VLOOKUP(E283,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M283" s="15"/>
-    </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A284" s="13"/>
-      <c r="B284" s="13"/>
-      <c r="C284" s="17"/>
-      <c r="E284" s="88"/>
-      <c r="F284" s="6" t="e">
-        <f>+VLOOKUP(E284,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G284" s="14"/>
-      <c r="H284" s="14"/>
-      <c r="I284" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J284" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K284" t="str">
-        <f>+IF(E284="","",VLOOKUP(E284,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L284" t="str">
-        <f>+IF(E284="","",VLOOKUP(E284,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M284" s="15"/>
-    </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A285" s="13"/>
-      <c r="B285" s="13"/>
-      <c r="C285" s="17"/>
-      <c r="E285" s="88"/>
-      <c r="F285" s="6" t="e">
-        <f>+VLOOKUP(E285,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G285" s="14"/>
-      <c r="H285" s="14"/>
-      <c r="I285" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J285" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K285" t="str">
-        <f>+IF(E285="","",VLOOKUP(E285,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L285" t="str">
-        <f>+IF(E285="","",VLOOKUP(E285,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M285" s="15"/>
-    </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A286" s="13"/>
-      <c r="B286" s="13"/>
-      <c r="C286" s="17"/>
-      <c r="E286" s="88"/>
-      <c r="F286" s="6" t="e">
-        <f>+VLOOKUP(E286,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G286" s="14"/>
-      <c r="H286" s="14"/>
-      <c r="I286" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J286" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K286" t="str">
-        <f>+IF(E286="","",VLOOKUP(E286,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L286" t="str">
-        <f>+IF(E286="","",VLOOKUP(E286,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M286" s="15"/>
-    </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A287" s="13"/>
-      <c r="B287" s="13"/>
-      <c r="C287" s="17"/>
-      <c r="E287" s="88"/>
-      <c r="F287" s="6" t="e">
-        <f>+VLOOKUP(E287,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G287" s="14"/>
-      <c r="H287" s="14"/>
-      <c r="I287" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J287" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K287" t="str">
-        <f>+IF(E287="","",VLOOKUP(E287,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L287" t="str">
-        <f>+IF(E287="","",VLOOKUP(E287,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M287" s="15"/>
-    </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A288" s="13"/>
-      <c r="B288" s="13"/>
-      <c r="C288" s="17"/>
-      <c r="E288" s="88"/>
-      <c r="F288" s="6" t="e">
-        <f>+VLOOKUP(E288,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G288" s="14"/>
-      <c r="H288" s="14"/>
-      <c r="I288" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J288" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K288" t="str">
-        <f>+IF(E288="","",VLOOKUP(E288,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L288" t="str">
-        <f>+IF(E288="","",VLOOKUP(E288,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M288" s="15"/>
-    </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A289" s="13"/>
-      <c r="B289" s="13"/>
-      <c r="C289" s="17"/>
-      <c r="E289" s="88"/>
-      <c r="F289" s="6" t="e">
-        <f>+VLOOKUP(E289,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G289" s="14"/>
-      <c r="H289" s="14"/>
-      <c r="I289" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J289" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K289" t="str">
-        <f>+IF(E289="","",VLOOKUP(E289,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L289" t="str">
-        <f>+IF(E289="","",VLOOKUP(E289,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M289" s="15"/>
-    </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A290" s="13"/>
-      <c r="B290" s="13"/>
-      <c r="C290" s="17"/>
-      <c r="E290" s="88"/>
-      <c r="F290" s="6" t="e">
-        <f>+VLOOKUP(E290,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G290" s="14"/>
-      <c r="H290" s="14"/>
-      <c r="I290" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J290" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K290" t="str">
-        <f>+IF(E290="","",VLOOKUP(E290,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L290" t="str">
-        <f>+IF(E290="","",VLOOKUP(E290,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M290" s="15"/>
-    </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A291" s="13"/>
-      <c r="B291" s="13"/>
-      <c r="C291" s="17"/>
-      <c r="E291" s="88"/>
-      <c r="F291" s="6" t="e">
-        <f>+VLOOKUP(E291,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G291" s="14"/>
-      <c r="H291" s="14"/>
-      <c r="I291" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J291" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K291" t="str">
-        <f>+IF(E291="","",VLOOKUP(E291,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L291" t="str">
-        <f>+IF(E291="","",VLOOKUP(E291,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M291" s="15"/>
-    </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A292" s="13"/>
-      <c r="B292" s="13"/>
-      <c r="C292" s="17"/>
-      <c r="E292" s="88"/>
-      <c r="F292" s="6" t="e">
-        <f>+VLOOKUP(E292,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G292" s="14"/>
-      <c r="H292" s="14"/>
-      <c r="I292" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J292" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K292" t="str">
-        <f>+IF(E292="","",VLOOKUP(E292,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L292" t="str">
-        <f>+IF(E292="","",VLOOKUP(E292,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M292" s="15"/>
-    </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A293" s="13"/>
-      <c r="B293" s="13"/>
-      <c r="C293" s="17"/>
-      <c r="E293" s="88"/>
-      <c r="F293" s="6" t="e">
-        <f>+VLOOKUP(E293,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G293" s="14"/>
-      <c r="H293" s="14"/>
-      <c r="I293" s="16">
-        <v>46274</v>
-      </c>
-      <c r="J293" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K293" t="str">
-        <f>+IF(E293="","",VLOOKUP(E293,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L293" t="str">
-        <f>+IF(E293="","",VLOOKUP(E293,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M293" s="15"/>
-    </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A294" s="13"/>
-      <c r="B294" s="13"/>
-      <c r="C294" s="17"/>
-      <c r="E294" s="88"/>
-      <c r="F294" s="6" t="e">
-        <f>+VLOOKUP(E294,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G294" s="14"/>
-      <c r="H294" s="14"/>
-      <c r="I294" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J294" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K294" t="str">
-        <f>+IF(E294="","",VLOOKUP(E294,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L294" t="str">
-        <f>+IF(E294="","",VLOOKUP(E294,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M294" s="15"/>
-    </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A295" s="13"/>
-      <c r="B295" s="13"/>
-      <c r="C295" s="17"/>
-      <c r="E295" s="88"/>
-      <c r="F295" s="6" t="e">
-        <f>+VLOOKUP(E295,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G295" s="14"/>
-      <c r="H295" s="14"/>
-      <c r="I295" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J295" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K295" t="str">
-        <f>+IF(E295="","",VLOOKUP(E295,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L295" t="str">
-        <f>+IF(E295="","",VLOOKUP(E295,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M295" s="15"/>
-    </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A296" s="13"/>
-      <c r="B296" s="13"/>
-      <c r="C296" s="17"/>
-      <c r="E296" s="88"/>
-      <c r="F296" s="6" t="e">
-        <f>+VLOOKUP(E296,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G296" s="14"/>
-      <c r="H296" s="14"/>
-      <c r="I296" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J296" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K296" t="str">
-        <f>+IF(E296="","",VLOOKUP(E296,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L296" t="str">
-        <f>+IF(E296="","",VLOOKUP(E296,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M296" s="15"/>
-    </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A297" s="13"/>
-      <c r="B297" s="13"/>
-      <c r="C297" s="17"/>
-      <c r="E297" s="88"/>
-      <c r="F297" s="6" t="e">
-        <f>+VLOOKUP(E297,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G297" s="14"/>
-      <c r="H297" s="14"/>
-      <c r="I297" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J297" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K297" t="str">
-        <f>+IF(E297="","",VLOOKUP(E297,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L297" t="str">
-        <f>+IF(E297="","",VLOOKUP(E297,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M297" s="15"/>
-    </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A298" s="13"/>
-      <c r="B298" s="13"/>
-      <c r="C298" s="17"/>
-      <c r="E298" s="88"/>
-      <c r="F298" s="6" t="e">
-        <f>+VLOOKUP(E298,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G298" s="14"/>
-      <c r="H298" s="14"/>
-      <c r="I298" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J298" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K298" t="str">
-        <f>+IF(E298="","",VLOOKUP(E298,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L298" t="str">
-        <f>+IF(E298="","",VLOOKUP(E298,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M298" s="15"/>
-    </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A299" s="13"/>
-      <c r="B299" s="13"/>
-      <c r="C299" s="17"/>
-      <c r="E299" s="88"/>
-      <c r="F299" s="6" t="e">
-        <f>+VLOOKUP(E299,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G299" s="14"/>
-      <c r="H299" s="14"/>
-      <c r="I299" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J299" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K299" t="str">
-        <f>+IF(E299="","",VLOOKUP(E299,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L299" t="str">
-        <f>+IF(E299="","",VLOOKUP(E299,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M299" s="15"/>
-    </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A300" s="13"/>
-      <c r="B300" s="13"/>
-      <c r="C300" s="17"/>
-      <c r="E300" s="88"/>
-      <c r="F300" s="6" t="e">
-        <f>+VLOOKUP(E300,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G300" s="14"/>
-      <c r="H300" s="14"/>
-      <c r="I300" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J300" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K300" t="str">
-        <f>+IF(E300="","",VLOOKUP(E300,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L300" t="str">
-        <f>+IF(E300="","",VLOOKUP(E300,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M300" s="15"/>
-    </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A301" s="13"/>
-      <c r="B301" s="13"/>
-      <c r="C301" s="17"/>
-      <c r="E301" s="88"/>
-      <c r="F301" s="6" t="e">
-        <f>+VLOOKUP(E301,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G301" s="14"/>
-      <c r="H301" s="14"/>
-      <c r="I301" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J301" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K301" t="str">
-        <f>+IF(E301="","",VLOOKUP(E301,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L301" t="str">
-        <f>+IF(E301="","",VLOOKUP(E301,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M301" s="15"/>
-    </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A302" s="13"/>
-      <c r="B302" s="13"/>
-      <c r="C302" s="17"/>
-      <c r="E302" s="88"/>
-      <c r="F302" s="6" t="e">
-        <f>+VLOOKUP(E302,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G302" s="14"/>
-      <c r="H302" s="14"/>
-      <c r="I302" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J302" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K302" t="str">
-        <f>+IF(E302="","",VLOOKUP(E302,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L302" t="str">
-        <f>+IF(E302="","",VLOOKUP(E302,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M302" s="15"/>
-    </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A303" s="13"/>
-      <c r="B303" s="13"/>
-      <c r="C303" s="17"/>
-      <c r="E303" s="88"/>
-      <c r="F303" s="6" t="e">
-        <f>+VLOOKUP(E303,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G303" s="14"/>
-      <c r="H303" s="14"/>
-      <c r="I303" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J303" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K303" t="str">
-        <f>+IF(E303="","",VLOOKUP(E303,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L303" t="str">
-        <f>+IF(E303="","",VLOOKUP(E303,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M303" s="15"/>
-    </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A304" s="13"/>
-      <c r="B304" s="13"/>
-      <c r="C304" s="17"/>
-      <c r="E304" s="88"/>
-      <c r="F304" s="6" t="e">
-        <f>+VLOOKUP(E304,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G304" s="14"/>
-      <c r="H304" s="14"/>
-      <c r="I304" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J304" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K304" t="str">
-        <f>+IF(E304="","",VLOOKUP(E304,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L304" t="str">
-        <f>+IF(E304="","",VLOOKUP(E304,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M304" s="15"/>
-    </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A305" s="13"/>
-      <c r="B305" s="13"/>
-      <c r="C305" s="17"/>
-      <c r="E305" s="88"/>
-      <c r="F305" s="6" t="e">
-        <f>+VLOOKUP(E305,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G305" s="14"/>
-      <c r="H305" s="14"/>
-      <c r="I305" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J305" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K305" t="str">
-        <f>+IF(E305="","",VLOOKUP(E305,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L305" t="str">
-        <f>+IF(E305="","",VLOOKUP(E305,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M305" s="15"/>
-    </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A306" s="13"/>
-      <c r="B306" s="13"/>
-      <c r="C306" s="17"/>
-      <c r="E306" s="88"/>
-      <c r="F306" s="6" t="e">
-        <f>+VLOOKUP(E306,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G306" s="14"/>
-      <c r="H306" s="14"/>
-      <c r="I306" s="16">
-        <v>46275</v>
-      </c>
-      <c r="J306" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K306" t="str">
-        <f>+IF(E306="","",VLOOKUP(E306,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L306" t="str">
-        <f>+IF(E306="","",VLOOKUP(E306,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M306" s="15"/>
-    </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A307" s="13"/>
-      <c r="B307" s="13"/>
-      <c r="C307" s="17"/>
-      <c r="E307" s="88"/>
-      <c r="F307" s="6" t="e">
-        <f>+VLOOKUP(E307,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G307" s="14"/>
-      <c r="H307" s="14"/>
-      <c r="I307" s="16">
-        <v>46276</v>
-      </c>
-      <c r="J307" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K307" t="str">
-        <f>+IF(E307="","",VLOOKUP(E307,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L307" t="str">
-        <f>+IF(E307="","",VLOOKUP(E307,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M307" s="15"/>
-    </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A308" s="13"/>
-      <c r="B308" s="13"/>
-      <c r="C308" s="17"/>
-      <c r="E308" s="88"/>
-      <c r="F308" s="6" t="e">
-        <f>+VLOOKUP(E308,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G308" s="14"/>
-      <c r="H308" s="14"/>
-      <c r="I308" s="16">
-        <v>46276</v>
-      </c>
-      <c r="J308" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K308" t="str">
-        <f>+IF(E308="","",VLOOKUP(E308,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L308" t="str">
-        <f>+IF(E308="","",VLOOKUP(E308,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M308" s="15"/>
-    </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A309" s="13"/>
-      <c r="B309" s="13"/>
-      <c r="C309" s="17"/>
-      <c r="E309" s="88"/>
-      <c r="F309" s="6" t="e">
-        <f>+VLOOKUP(E309,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G309" s="14"/>
-      <c r="H309" s="14"/>
-      <c r="I309" s="16">
-        <v>46276</v>
-      </c>
-      <c r="J309" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K309" t="str">
-        <f>+IF(E309="","",VLOOKUP(E309,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L309" t="str">
-        <f>+IF(E309="","",VLOOKUP(E309,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M309" s="15"/>
-    </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A310" s="13"/>
-      <c r="B310" s="13"/>
-      <c r="C310" s="17"/>
-      <c r="E310" s="88"/>
-      <c r="F310" s="6" t="e">
-        <f>+VLOOKUP(E310,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G310" s="14"/>
-      <c r="H310" s="14"/>
-      <c r="I310" s="16">
-        <v>46276</v>
-      </c>
-      <c r="J310" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K310" t="str">
-        <f>+IF(E310="","",VLOOKUP(E310,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L310" t="str">
-        <f>+IF(E310="","",VLOOKUP(E310,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M310" s="15"/>
-    </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A311" s="13"/>
-      <c r="B311" s="13"/>
-      <c r="C311" s="17"/>
-      <c r="E311" s="88"/>
-      <c r="F311" s="6" t="e">
-        <f>+VLOOKUP(E311,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G311" s="14"/>
-      <c r="H311" s="14"/>
-      <c r="I311" s="16">
-        <v>46276</v>
-      </c>
-      <c r="J311" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K311" t="str">
-        <f>+IF(E311="","",VLOOKUP(E311,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L311" t="str">
-        <f>+IF(E311="","",VLOOKUP(E311,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M311" s="15"/>
-    </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A312" s="13"/>
-      <c r="B312" s="13"/>
-      <c r="C312" s="17"/>
-      <c r="E312" s="88"/>
-      <c r="F312" s="6" t="e">
-        <f>+VLOOKUP(E312,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G312" s="14"/>
-      <c r="H312" s="14"/>
-      <c r="I312" s="16">
-        <v>46277</v>
-      </c>
-      <c r="J312" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K312" t="str">
-        <f>+IF(E312="","",VLOOKUP(E312,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L312" t="str">
-        <f>+IF(E312="","",VLOOKUP(E312,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M312" s="15"/>
-    </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A313" s="13"/>
-      <c r="B313" s="13"/>
-      <c r="C313" s="17"/>
-      <c r="E313" s="88"/>
-      <c r="F313" s="6" t="e">
-        <f>+VLOOKUP(E313,CATALOGO!G:L,6,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G313" s="14"/>
-      <c r="H313" s="14"/>
-      <c r="I313" s="16">
-        <v>46277</v>
-      </c>
-      <c r="J313" s="12">
-        <f t="shared" si="5"/>
-        <v>37</v>
-      </c>
-      <c r="K313" t="str">
-        <f>+IF(E313="","",VLOOKUP(E313,CATALOGO!G:I,2,0))</f>
-        <v/>
-      </c>
-      <c r="L313" t="str">
-        <f>+IF(E313="","",VLOOKUP(E313,CATALOGO!G:I,3,0))</f>
-        <v/>
-      </c>
-      <c r="M313" s="15"/>
-    </row>
+    <row r="169" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:N313" xr:uid="{F6943C4E-D0C1-4399-9277-8C3BA29014B7}"/>
-  <conditionalFormatting sqref="M2:M313">
+  <autoFilter ref="A1:N168" xr:uid="{F6943C4E-D0C1-4399-9277-8C3BA29014B7}"/>
+  <conditionalFormatting sqref="M2:M168">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>#REF!</formula>
     </cfRule>
@@ -27170,6 +23111,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9ec7a165-d323-4302-8043-ea580ce1e37b" xsi:nil="true"/>
+    <_ModernAudienceTargetUserField xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ModernAudienceTargetUserField>
+    <Audiencias_x0020_de_x0020_destino xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A8528D2613016E4F8BB018856F73371D" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c3609afe6843af7a81bebb55ab3705b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac" xmlns:ns3="9ec7a165-d323-4302-8043-ea580ce1e37b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e700fe5959ff58d73b586561e52d5093" ns2:_="" ns3:_="">
     <xsd:import namespace="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac"/>
@@ -27420,36 +23390,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9ec7a165-d323-4302-8043-ea580ce1e37b" xsi:nil="true"/>
-    <_ModernAudienceTargetUserField xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ModernAudienceTargetUserField>
-    <Audiencias_x0020_de_x0020_destino xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AE2DB07-E1EE-4AEB-80E7-74D3285DBEFE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA9869F1-282E-4391-9BF8-BCB60A0A8B6F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac"/>
+    <ds:schemaRef ds:uri="9ec7a165-d323-4302-8043-ea580ce1e37b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D82F03D-D48B-4420-853D-E4A8C58AE522}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27466,23 +23426,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA9869F1-282E-4391-9BF8-BCB60A0A8B6F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac"/>
-    <ds:schemaRef ds:uri="9ec7a165-d323-4302-8043-ea580ce1e37b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AE2DB07-E1EE-4AEB-80E7-74D3285DBEFE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/PLANEACION_SEMANAL 1.xlsx
+++ b/PLANEACION_SEMANAL 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chanitosfrutas.sharepoint.com/sites/04.Logstica/Documentos compartidos/General/Pre-enfrío/09. Desarrollos/Planeacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="510" documentId="8_{545E5EC0-B69F-4327-BF2C-9EFD71AFF5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E9D9929-7A35-4D6C-A479-5EB0300DA938}"/>
+  <xr:revisionPtr revIDLastSave="513" documentId="8_{545E5EC0-B69F-4327-BF2C-9EFD71AFF5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA2B99E0-FBBD-471A-BA62-1AB6D336648C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D41B2D9D-66D1-4881-AE1E-852E308D9588}"/>
   </bookViews>
@@ -5409,7 +5409,7 @@
         <v>8</v>
       </c>
       <c r="G3" s="14">
-        <v>384</v>
+        <v>960</v>
       </c>
       <c r="H3" s="14">
         <v>8</v>
@@ -5973,7 +5973,7 @@
         <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H15" s="14">
         <v>1.75</v>
@@ -6021,7 +6021,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="14">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="H16" s="14">
         <v>22.25</v>
@@ -23111,35 +23111,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac" xsi:nil="true"/>
-    <TaxCatchAll xmlns="9ec7a165-d323-4302-8043-ea580ce1e37b" xsi:nil="true"/>
-    <_ModernAudienceTargetUserField xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ModernAudienceTargetUserField>
-    <Audiencias_x0020_de_x0020_destino xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A8528D2613016E4F8BB018856F73371D" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5c3609afe6843af7a81bebb55ab3705b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac" xmlns:ns3="9ec7a165-d323-4302-8043-ea580ce1e37b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e700fe5959ff58d73b586561e52d5093" ns2:_="" ns3:_="">
     <xsd:import namespace="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac"/>
@@ -23390,10 +23361,50 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac" xsi:nil="true"/>
+    <TaxCatchAll xmlns="9ec7a165-d323-4302-8043-ea580ce1e37b" xsi:nil="true"/>
+    <_ModernAudienceTargetUserField xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ModernAudienceTargetUserField>
+    <Audiencias_x0020_de_x0020_destino xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AE2DB07-E1EE-4AEB-80E7-74D3285DBEFE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D82F03D-D48B-4420-853D-E4A8C58AE522}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac"/>
+    <ds:schemaRef ds:uri="9ec7a165-d323-4302-8043-ea580ce1e37b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -23410,20 +23421,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D82F03D-D48B-4420-853D-E4A8C58AE522}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AE2DB07-E1EE-4AEB-80E7-74D3285DBEFE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3d83bf51-5c87-4fb0-ba13-134b9ccf2aac"/>
-    <ds:schemaRef ds:uri="9ec7a165-d323-4302-8043-ea580ce1e37b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>